--- a/research/traditional_assets/database/data/malta/malta_recreation.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09477234861913209</v>
+        <v>0.09446989539896514</v>
       </c>
       <c r="C2">
-        <v>38.31245171317712</v>
+        <v>38.03371689918485</v>
       </c>
       <c r="D2">
-        <v>30.66245171317712</v>
+        <v>30.83571689918485</v>
       </c>
       <c r="E2">
-        <v>-22.4</v>
+        <v>-21.948</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="G2">
         <v>7.65</v>
@@ -1451,28 +1451,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0227356</v>
       </c>
       <c r="N2">
-        <v>3.073666666666667</v>
+        <v>3.050931066666667</v>
       </c>
       <c r="O2">
-        <v>1.075783333333333</v>
+        <v>1.067825873333333</v>
       </c>
       <c r="P2">
-        <v>1.997883333333333</v>
+        <v>1.983105193333333</v>
       </c>
       <c r="Q2">
-        <v>2.440883333333333</v>
+        <v>2.426105193333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09477234861913209</v>
+        <v>0.09509388424137892</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378594</v>
+        <v>0.9028348011779564</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.1917990581584</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09446989539896514</v>
+        <v>0.09416744217879816</v>
       </c>
       <c r="C3">
-        <v>38.03371689918485</v>
+        <v>37.75695136204787</v>
       </c>
       <c r="D3">
-        <v>30.83571689918485</v>
+        <v>31.01095136204788</v>
       </c>
       <c r="E3">
-        <v>-21.948</v>
+        <v>-21.496</v>
       </c>
       <c r="F3">
-        <v>0.452</v>
+        <v>0.904</v>
       </c>
       <c r="G3">
         <v>7.65</v>
@@ -1533,28 +1533,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0227356</v>
+        <v>0.0454712</v>
       </c>
       <c r="N3">
-        <v>3.050931066666667</v>
+        <v>3.028195466666666</v>
       </c>
       <c r="O3">
-        <v>1.067825873333333</v>
+        <v>1.059868413333333</v>
       </c>
       <c r="P3">
-        <v>1.983105193333333</v>
+        <v>1.968327053333333</v>
       </c>
       <c r="Q3">
-        <v>2.426105193333334</v>
+        <v>2.411327053333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09509388424137892</v>
+        <v>0.09542198181510017</v>
       </c>
       <c r="T3">
-        <v>0.9028348011779564</v>
+        <v>0.9088440234637698</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.1917990581584</v>
+        <v>67.5958995290792</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09416744217879816</v>
+        <v>0.09386498895863121</v>
       </c>
       <c r="C4">
-        <v>37.75695136204787</v>
+        <v>37.48218886690729</v>
       </c>
       <c r="D4">
-        <v>31.01095136204788</v>
+        <v>31.18818886690729</v>
       </c>
       <c r="E4">
-        <v>-21.496</v>
+        <v>-21.044</v>
       </c>
       <c r="F4">
-        <v>0.904</v>
+        <v>1.356</v>
       </c>
       <c r="G4">
         <v>7.65</v>
@@ -1615,28 +1615,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0454712</v>
+        <v>0.0682068</v>
       </c>
       <c r="N4">
-        <v>3.028195466666666</v>
+        <v>3.005459866666667</v>
       </c>
       <c r="O4">
-        <v>1.059868413333333</v>
+        <v>1.051910953333333</v>
       </c>
       <c r="P4">
-        <v>1.968327053333333</v>
+        <v>1.953548913333333</v>
       </c>
       <c r="Q4">
-        <v>2.411327053333333</v>
+        <v>2.396548913333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09542198181510017</v>
+        <v>0.09575684428724866</v>
       </c>
       <c r="T4">
-        <v>0.9088440234637698</v>
+        <v>0.9149771472400121</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.5958995290792</v>
+        <v>45.06393301938614</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09386498895863121</v>
+        <v>0.09356253573846424</v>
       </c>
       <c r="C5">
-        <v>37.48218886690729</v>
+        <v>37.20946395525564</v>
       </c>
       <c r="D5">
-        <v>31.18818886690729</v>
+        <v>31.36746395525564</v>
       </c>
       <c r="E5">
-        <v>-21.044</v>
+        <v>-20.592</v>
       </c>
       <c r="F5">
-        <v>1.356</v>
+        <v>1.808</v>
       </c>
       <c r="G5">
         <v>7.65</v>
@@ -1697,28 +1697,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M5">
-        <v>0.0682068</v>
+        <v>0.09094239999999999</v>
       </c>
       <c r="N5">
-        <v>3.005459866666667</v>
+        <v>2.982724266666667</v>
       </c>
       <c r="O5">
-        <v>1.051910953333333</v>
+        <v>1.043953493333333</v>
       </c>
       <c r="P5">
-        <v>1.953548913333333</v>
+        <v>1.938770773333333</v>
       </c>
       <c r="Q5">
-        <v>2.396548913333333</v>
+        <v>2.381770773333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09575684428724866</v>
+        <v>0.09609868306090025</v>
       </c>
       <c r="T5">
-        <v>0.9149771472400121</v>
+        <v>0.9212380444282597</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.06393301938614</v>
+        <v>33.79794976453961</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09356253573846424</v>
+        <v>0.09326008251829727</v>
       </c>
       <c r="C6">
-        <v>37.20946395525564</v>
+        <v>36.93881196737887</v>
       </c>
       <c r="D6">
-        <v>31.36746395525564</v>
+        <v>31.54881196737886</v>
       </c>
       <c r="E6">
-        <v>-20.592</v>
+        <v>-20.14</v>
       </c>
       <c r="F6">
-        <v>1.808</v>
+        <v>2.26</v>
       </c>
       <c r="G6">
         <v>7.65</v>
@@ -1779,28 +1779,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M6">
-        <v>0.09094239999999999</v>
+        <v>0.113678</v>
       </c>
       <c r="N6">
-        <v>2.982724266666667</v>
+        <v>2.959988666666666</v>
       </c>
       <c r="O6">
-        <v>1.043953493333333</v>
+        <v>1.035996033333333</v>
       </c>
       <c r="P6">
-        <v>1.938770773333333</v>
+        <v>1.923992633333333</v>
       </c>
       <c r="Q6">
-        <v>2.381770773333333</v>
+        <v>2.366992633333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09609868306090025</v>
+        <v>0.09644771844031293</v>
       </c>
       <c r="T6">
-        <v>0.9212380444282597</v>
+        <v>0.927630749978365</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.79794976453961</v>
+        <v>27.03835981163168</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09326008251829727</v>
+        <v>0.09295762929813031</v>
       </c>
       <c r="C7">
-        <v>36.93881196737887</v>
+        <v>36.67026906558134</v>
       </c>
       <c r="D7">
-        <v>31.54881196737886</v>
+        <v>31.73226906558135</v>
       </c>
       <c r="E7">
-        <v>-20.14</v>
+        <v>-19.688</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>2.712</v>
       </c>
       <c r="G7">
         <v>7.65</v>
@@ -1861,28 +1861,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M7">
-        <v>0.113678</v>
+        <v>0.1364136</v>
       </c>
       <c r="N7">
-        <v>2.959988666666666</v>
+        <v>2.937253066666667</v>
       </c>
       <c r="O7">
-        <v>1.035996033333333</v>
+        <v>1.028038573333333</v>
       </c>
       <c r="P7">
-        <v>1.923992633333333</v>
+        <v>1.909214493333333</v>
       </c>
       <c r="Q7">
-        <v>2.366992633333333</v>
+        <v>2.352214493333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09644771844031293</v>
+        <v>0.09680418010439396</v>
       </c>
       <c r="T7">
-        <v>0.927630749978365</v>
+        <v>0.9341594705401748</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.03835981163168</v>
+        <v>22.53196650969307</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09295762929813031</v>
+        <v>0.09265517607796336</v>
       </c>
       <c r="C8">
-        <v>36.67026906558134</v>
+        <v>36.403872258226</v>
       </c>
       <c r="D8">
-        <v>31.73226906558135</v>
+        <v>31.91787225822601</v>
       </c>
       <c r="E8">
-        <v>-19.688</v>
+        <v>-19.236</v>
       </c>
       <c r="F8">
-        <v>2.712</v>
+        <v>3.164</v>
       </c>
       <c r="G8">
         <v>7.65</v>
@@ -1943,28 +1943,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M8">
-        <v>0.1364136</v>
+        <v>0.1591492</v>
       </c>
       <c r="N8">
-        <v>2.937253066666667</v>
+        <v>2.914517466666667</v>
       </c>
       <c r="O8">
-        <v>1.028038573333333</v>
+        <v>1.020081113333333</v>
       </c>
       <c r="P8">
-        <v>1.909214493333333</v>
+        <v>1.894436353333333</v>
       </c>
       <c r="Q8">
-        <v>2.352214493333333</v>
+        <v>2.337436353333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09680418010439396</v>
+        <v>0.09716830761071328</v>
       </c>
       <c r="T8">
-        <v>0.9341594705401748</v>
+        <v>0.9408285936947115</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.53196650969307</v>
+        <v>19.31311415116549</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09265517607796335</v>
+        <v>0.0923527228577964</v>
       </c>
       <c r="C9">
-        <v>36.40387225822602</v>
+        <v>36.139659424623</v>
       </c>
       <c r="D9">
-        <v>31.91787225822602</v>
+        <v>32.105659424623</v>
       </c>
       <c r="E9">
-        <v>-19.236</v>
+        <v>-18.784</v>
       </c>
       <c r="F9">
-        <v>3.164000000000001</v>
+        <v>3.616</v>
       </c>
       <c r="G9">
         <v>7.65</v>
@@ -2025,28 +2025,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M9">
-        <v>0.1591492</v>
+        <v>0.1818848</v>
       </c>
       <c r="N9">
-        <v>2.914517466666667</v>
+        <v>2.891781866666666</v>
       </c>
       <c r="O9">
-        <v>1.020081113333333</v>
+        <v>1.012123653333333</v>
       </c>
       <c r="P9">
-        <v>1.894436353333333</v>
+        <v>1.879658213333333</v>
       </c>
       <c r="Q9">
-        <v>2.337436353333334</v>
+        <v>2.322658213333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09716830761071328</v>
+        <v>0.09754035093238739</v>
       </c>
       <c r="T9">
-        <v>0.9408285936947115</v>
+        <v>0.9476426977873904</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.31311415116549</v>
+        <v>16.8989748822698</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0923527228577964</v>
+        <v>0.09205026963762944</v>
       </c>
       <c r="C10">
-        <v>36.139659424623</v>
+        <v>35.87766934080218</v>
       </c>
       <c r="D10">
-        <v>32.105659424623</v>
+        <v>32.29566934080218</v>
       </c>
       <c r="E10">
-        <v>-18.784</v>
+        <v>-18.332</v>
       </c>
       <c r="F10">
-        <v>3.616</v>
+        <v>4.068000000000001</v>
       </c>
       <c r="G10">
         <v>7.65</v>
@@ -2107,28 +2107,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M10">
-        <v>0.1818848</v>
+        <v>0.2046204</v>
       </c>
       <c r="N10">
-        <v>2.891781866666666</v>
+        <v>2.869046266666667</v>
       </c>
       <c r="O10">
-        <v>1.012123653333333</v>
+        <v>1.004166193333333</v>
       </c>
       <c r="P10">
-        <v>1.879658213333333</v>
+        <v>1.864880073333333</v>
       </c>
       <c r="Q10">
-        <v>2.322658213333333</v>
+        <v>2.307880073333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09754035093238739</v>
+        <v>0.09792057103036202</v>
       </c>
       <c r="T10">
-        <v>0.9476426977873904</v>
+        <v>0.9546065624095789</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.8989748822698</v>
+        <v>15.02131100646205</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09205026963762944</v>
+        <v>0.09174781641746246</v>
       </c>
       <c r="C11">
-        <v>35.87766934080218</v>
+        <v>35.61794170620628</v>
       </c>
       <c r="D11">
-        <v>32.29566934080218</v>
+        <v>32.48794170620628</v>
       </c>
       <c r="E11">
-        <v>-18.332</v>
+        <v>-17.88</v>
       </c>
       <c r="F11">
-        <v>4.068000000000001</v>
+        <v>4.52</v>
       </c>
       <c r="G11">
         <v>7.65</v>
@@ -2189,28 +2189,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M11">
-        <v>0.2046204</v>
+        <v>0.227356</v>
       </c>
       <c r="N11">
-        <v>2.869046266666667</v>
+        <v>2.846310666666667</v>
       </c>
       <c r="O11">
-        <v>1.004166193333333</v>
+        <v>0.9962087333333333</v>
       </c>
       <c r="P11">
-        <v>1.864880073333333</v>
+        <v>1.850101933333333</v>
       </c>
       <c r="Q11">
-        <v>2.307880073333333</v>
+        <v>2.293101933333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09792057103036202</v>
+        <v>0.09830924046384719</v>
       </c>
       <c r="T11">
-        <v>0.9546065624095789</v>
+        <v>0.961725179578927</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.02131100646205</v>
+        <v>13.51917990581584</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09174781641746246</v>
+        <v>0.09155261319729552</v>
       </c>
       <c r="C12">
-        <v>35.61794170620627</v>
+        <v>35.29125452065457</v>
       </c>
       <c r="D12">
-        <v>32.48794170620628</v>
+        <v>32.61325452065457</v>
       </c>
       <c r="E12">
-        <v>-17.88</v>
+        <v>-17.428</v>
       </c>
       <c r="F12">
-        <v>4.52</v>
+        <v>4.972</v>
       </c>
       <c r="G12">
         <v>7.65</v>
@@ -2271,45 +2271,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M12">
-        <v>0.227356</v>
+        <v>0.2575496</v>
       </c>
       <c r="N12">
-        <v>2.846310666666667</v>
+        <v>2.816117066666667</v>
       </c>
       <c r="O12">
-        <v>0.9962087333333333</v>
+        <v>0.9856409733333332</v>
       </c>
       <c r="P12">
-        <v>1.850101933333333</v>
+        <v>1.830476093333333</v>
       </c>
       <c r="Q12">
-        <v>2.293101933333333</v>
+        <v>2.273476093333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09830924046384719</v>
+        <v>0.09870664404190507</v>
       </c>
       <c r="T12">
-        <v>0.961725179578927</v>
+        <v>0.9690037656734291</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.51917990581584</v>
+        <v>11.93427078382831</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09155261319729552</v>
+        <v>0.09125990997712854</v>
       </c>
       <c r="C13">
-        <v>35.29125452065457</v>
+        <v>35.02898063708177</v>
       </c>
       <c r="D13">
-        <v>32.61325452065457</v>
+        <v>32.80298063708177</v>
       </c>
       <c r="E13">
-        <v>-17.428</v>
+        <v>-16.976</v>
       </c>
       <c r="F13">
-        <v>4.972</v>
+        <v>5.424</v>
       </c>
       <c r="G13">
         <v>7.65</v>
@@ -2353,28 +2353,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M13">
-        <v>0.2575496</v>
+        <v>0.2809632</v>
       </c>
       <c r="N13">
-        <v>2.816117066666667</v>
+        <v>2.792703466666667</v>
       </c>
       <c r="O13">
-        <v>0.9856409733333332</v>
+        <v>0.9774462133333333</v>
       </c>
       <c r="P13">
-        <v>1.830476093333333</v>
+        <v>1.815257253333333</v>
       </c>
       <c r="Q13">
-        <v>2.273476093333334</v>
+        <v>2.258257253333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09870664404190507</v>
+        <v>0.09911307951946426</v>
       </c>
       <c r="T13">
-        <v>0.9690037656734291</v>
+        <v>0.9764477741791696</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.93427078382831</v>
+        <v>10.93974821850928</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09125990997712854</v>
+        <v>0.09096720675696157</v>
       </c>
       <c r="C14">
-        <v>35.02898063708177</v>
+        <v>34.76892711637667</v>
       </c>
       <c r="D14">
-        <v>32.80298063708177</v>
+        <v>32.99492711637667</v>
       </c>
       <c r="E14">
-        <v>-16.976</v>
+        <v>-16.524</v>
       </c>
       <c r="F14">
-        <v>5.424</v>
+        <v>5.876</v>
       </c>
       <c r="G14">
         <v>7.65</v>
@@ -2435,28 +2435,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M14">
-        <v>0.2809632</v>
+        <v>0.3043768</v>
       </c>
       <c r="N14">
-        <v>2.792703466666667</v>
+        <v>2.769289866666667</v>
       </c>
       <c r="O14">
-        <v>0.9774462133333333</v>
+        <v>0.9692514533333332</v>
       </c>
       <c r="P14">
-        <v>1.815257253333333</v>
+        <v>1.800038413333333</v>
       </c>
       <c r="Q14">
-        <v>2.258257253333333</v>
+        <v>2.243038413333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09911307951946426</v>
+        <v>0.09952885834133515</v>
       </c>
       <c r="T14">
-        <v>0.9764477741791696</v>
+        <v>0.9840629093172261</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.93974821850928</v>
+        <v>10.0982291247778</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09096720675696157</v>
+        <v>0.09082920353679462</v>
       </c>
       <c r="C15">
-        <v>34.76892711637667</v>
+        <v>34.40820709861021</v>
       </c>
       <c r="D15">
-        <v>32.99492711637667</v>
+        <v>33.08620709861022</v>
       </c>
       <c r="E15">
-        <v>-16.524</v>
+        <v>-16.072</v>
       </c>
       <c r="F15">
-        <v>5.876</v>
+        <v>6.328000000000001</v>
       </c>
       <c r="G15">
         <v>7.65</v>
@@ -2517,45 +2517,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M15">
-        <v>0.3043768</v>
+        <v>0.3385480000000001</v>
       </c>
       <c r="N15">
-        <v>2.769289866666667</v>
+        <v>2.735118666666667</v>
       </c>
       <c r="O15">
-        <v>0.9692514533333332</v>
+        <v>0.9572915333333333</v>
       </c>
       <c r="P15">
-        <v>1.800038413333333</v>
+        <v>1.777827133333334</v>
       </c>
       <c r="Q15">
-        <v>2.243038413333333</v>
+        <v>2.220827133333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09952885834133515</v>
+        <v>0.09995430643813329</v>
       </c>
       <c r="T15">
-        <v>0.9840629093172261</v>
+        <v>0.9918551406212841</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.0982291247778</v>
+        <v>9.07896861498714</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09082920353679462</v>
+        <v>0.09054755031662766</v>
       </c>
       <c r="C16">
-        <v>34.40820709861021</v>
+        <v>34.14407816764032</v>
       </c>
       <c r="D16">
-        <v>33.08620709861022</v>
+        <v>33.27407816764032</v>
       </c>
       <c r="E16">
-        <v>-16.072</v>
+        <v>-15.62</v>
       </c>
       <c r="F16">
-        <v>6.328000000000001</v>
+        <v>6.780000000000001</v>
       </c>
       <c r="G16">
         <v>7.65</v>
@@ -2599,28 +2599,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M16">
-        <v>0.3385480000000001</v>
+        <v>0.3627300000000001</v>
       </c>
       <c r="N16">
-        <v>2.735118666666667</v>
+        <v>2.710936666666667</v>
       </c>
       <c r="O16">
-        <v>0.9572915333333333</v>
+        <v>0.9488278333333332</v>
       </c>
       <c r="P16">
-        <v>1.777827133333334</v>
+        <v>1.762108833333333</v>
       </c>
       <c r="Q16">
-        <v>2.220827133333334</v>
+        <v>2.205108833333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09995430643813329</v>
+        <v>0.1003897650783855</v>
       </c>
       <c r="T16">
-        <v>0.9918551406212841</v>
+        <v>0.9998307185442609</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.07896861498714</v>
+        <v>8.473704040654663</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09054755031662766</v>
+        <v>0.09026589709646068</v>
       </c>
       <c r="C17">
-        <v>34.14407816764032</v>
+        <v>33.88209497063988</v>
       </c>
       <c r="D17">
-        <v>33.27407816764032</v>
+        <v>33.46409497063988</v>
       </c>
       <c r="E17">
-        <v>-15.62</v>
+        <v>-15.168</v>
       </c>
       <c r="F17">
-        <v>6.78</v>
+        <v>7.232</v>
       </c>
       <c r="G17">
         <v>7.65</v>
@@ -2681,28 +2681,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M17">
-        <v>0.36273</v>
+        <v>0.386912</v>
       </c>
       <c r="N17">
-        <v>2.710936666666667</v>
+        <v>2.686754666666666</v>
       </c>
       <c r="O17">
-        <v>0.9488278333333332</v>
+        <v>0.9403641333333331</v>
       </c>
       <c r="P17">
-        <v>1.762108833333333</v>
+        <v>1.746390533333333</v>
       </c>
       <c r="Q17">
-        <v>2.205108833333334</v>
+        <v>2.189390533333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1003897650783855</v>
+        <v>0.1008355917815008</v>
       </c>
       <c r="T17">
-        <v>0.9998307185442609</v>
+        <v>1.00799619117969</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.473704040654665</v>
+        <v>7.944097538113748</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09026589709646068</v>
+        <v>0.09007264387629371</v>
       </c>
       <c r="C18">
-        <v>33.88209497063988</v>
+        <v>33.56173322565702</v>
       </c>
       <c r="D18">
-        <v>33.46409497063988</v>
+        <v>33.59573322565702</v>
       </c>
       <c r="E18">
-        <v>-15.168</v>
+        <v>-14.716</v>
       </c>
       <c r="F18">
-        <v>7.232</v>
+        <v>7.684000000000001</v>
       </c>
       <c r="G18">
         <v>7.65</v>
@@ -2763,45 +2763,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M18">
-        <v>0.386912</v>
+        <v>0.4172412000000001</v>
       </c>
       <c r="N18">
-        <v>2.686754666666666</v>
+        <v>2.656425466666667</v>
       </c>
       <c r="O18">
-        <v>0.9403641333333331</v>
+        <v>0.9297489133333333</v>
       </c>
       <c r="P18">
-        <v>1.746390533333333</v>
+        <v>1.726676553333333</v>
       </c>
       <c r="Q18">
-        <v>2.189390533333333</v>
+        <v>2.169676553333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1008355917815008</v>
+        <v>0.1012921612967394</v>
       </c>
       <c r="T18">
-        <v>1.00799619117969</v>
+        <v>1.016358422191876</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.944097538113748</v>
+        <v>7.366642284287041</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09007264387629371</v>
+        <v>0.08979619065612675</v>
       </c>
       <c r="C19">
-        <v>33.56173322565702</v>
+        <v>33.29985544088414</v>
       </c>
       <c r="D19">
-        <v>33.59573322565702</v>
+        <v>33.78585544088414</v>
       </c>
       <c r="E19">
-        <v>-14.716</v>
+        <v>-14.264</v>
       </c>
       <c r="F19">
-        <v>7.684000000000001</v>
+        <v>8.136000000000001</v>
       </c>
       <c r="G19">
         <v>7.65</v>
@@ -2845,28 +2845,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M19">
-        <v>0.4172412000000001</v>
+        <v>0.4417848000000001</v>
       </c>
       <c r="N19">
-        <v>2.656425466666667</v>
+        <v>2.631881866666666</v>
       </c>
       <c r="O19">
-        <v>0.9297489133333333</v>
+        <v>0.9211586533333331</v>
       </c>
       <c r="P19">
-        <v>1.726676553333333</v>
+        <v>1.710723213333333</v>
       </c>
       <c r="Q19">
-        <v>2.169676553333333</v>
+        <v>2.153723213333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1012921612967394</v>
+        <v>0.1017598666538131</v>
       </c>
       <c r="T19">
-        <v>1.016358422191876</v>
+        <v>1.024924610058017</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.366642284287041</v>
+        <v>6.957384379604427</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08979619065612676</v>
+        <v>0.08951973743595983</v>
       </c>
       <c r="C20">
-        <v>33.29985544088412</v>
+        <v>33.04014175104196</v>
       </c>
       <c r="D20">
-        <v>33.78585544088413</v>
+        <v>33.97814175104196</v>
       </c>
       <c r="E20">
-        <v>-14.264</v>
+        <v>-13.812</v>
       </c>
       <c r="F20">
-        <v>8.136000000000001</v>
+        <v>8.588000000000001</v>
       </c>
       <c r="G20">
         <v>7.65</v>
@@ -2927,28 +2927,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M20">
-        <v>0.4417848000000001</v>
+        <v>0.4663284000000001</v>
       </c>
       <c r="N20">
-        <v>2.631881866666666</v>
+        <v>2.607338266666666</v>
       </c>
       <c r="O20">
-        <v>0.9211586533333331</v>
+        <v>0.9125683933333332</v>
       </c>
       <c r="P20">
-        <v>1.710723213333333</v>
+        <v>1.694769873333333</v>
       </c>
       <c r="Q20">
-        <v>2.153723213333333</v>
+        <v>2.137769873333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1017598666538131</v>
+        <v>0.1022391202913084</v>
       </c>
       <c r="T20">
-        <v>1.024924610058017</v>
+        <v>1.033702308735669</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.957384379604427</v>
+        <v>6.591206254362089</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08951973743595983</v>
+        <v>0.08924328421579285</v>
       </c>
       <c r="C21">
-        <v>33.04014175104196</v>
+        <v>32.7826293173349</v>
       </c>
       <c r="D21">
-        <v>33.97814175104196</v>
+        <v>34.1726293173349</v>
       </c>
       <c r="E21">
-        <v>-13.812</v>
+        <v>-13.36</v>
       </c>
       <c r="F21">
-        <v>8.588000000000001</v>
+        <v>9.040000000000001</v>
       </c>
       <c r="G21">
         <v>7.65</v>
@@ -3009,28 +3009,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M21">
-        <v>0.4663284000000001</v>
+        <v>0.4908720000000001</v>
       </c>
       <c r="N21">
-        <v>2.607338266666666</v>
+        <v>2.582794666666667</v>
       </c>
       <c r="O21">
-        <v>0.9125683933333332</v>
+        <v>0.9039781333333332</v>
       </c>
       <c r="P21">
-        <v>1.694769873333333</v>
+        <v>1.678816533333333</v>
       </c>
       <c r="Q21">
-        <v>2.137769873333333</v>
+        <v>2.121816533333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1022391202913084</v>
+        <v>0.1027303552697411</v>
       </c>
       <c r="T21">
-        <v>1.033702308735669</v>
+        <v>1.042699449880262</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.591206254362089</v>
+        <v>6.261645941643985</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08924328421579285</v>
+        <v>0.0891033309956259</v>
       </c>
       <c r="C22">
-        <v>32.7826293173349</v>
+        <v>32.42993912442672</v>
       </c>
       <c r="D22">
-        <v>34.1726293173349</v>
+        <v>34.27193912442673</v>
       </c>
       <c r="E22">
-        <v>-13.36</v>
+        <v>-12.908</v>
       </c>
       <c r="F22">
-        <v>9.040000000000001</v>
+        <v>9.492000000000001</v>
       </c>
       <c r="G22">
         <v>7.65</v>
@@ -3091,45 +3091,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M22">
-        <v>0.4908720000000001</v>
+        <v>0.5249076</v>
       </c>
       <c r="N22">
-        <v>2.582794666666667</v>
+        <v>2.548759066666666</v>
       </c>
       <c r="O22">
-        <v>0.9039781333333332</v>
+        <v>0.8920656733333332</v>
       </c>
       <c r="P22">
-        <v>1.678816533333333</v>
+        <v>1.656693393333333</v>
       </c>
       <c r="Q22">
-        <v>2.121816533333333</v>
+        <v>2.099693393333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1027303552697411</v>
+        <v>0.1032340265767416</v>
       </c>
       <c r="T22">
-        <v>1.042699449880262</v>
+        <v>1.051924366750034</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.261645941643985</v>
+        <v>5.855633766146015</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0891033309956259</v>
+        <v>0.08883337777545892</v>
       </c>
       <c r="C23">
-        <v>32.42993912442672</v>
+        <v>32.17113566778577</v>
       </c>
       <c r="D23">
-        <v>34.27193912442673</v>
+        <v>34.46513566778577</v>
       </c>
       <c r="E23">
-        <v>-12.908</v>
+        <v>-12.456</v>
       </c>
       <c r="F23">
-        <v>9.492000000000001</v>
+        <v>9.944000000000001</v>
       </c>
       <c r="G23">
         <v>7.65</v>
@@ -3173,28 +3173,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M23">
-        <v>0.5249076</v>
+        <v>0.5499032</v>
       </c>
       <c r="N23">
-        <v>2.548759066666666</v>
+        <v>2.523763466666666</v>
       </c>
       <c r="O23">
-        <v>0.8920656733333332</v>
+        <v>0.8833172133333331</v>
       </c>
       <c r="P23">
-        <v>1.656693393333333</v>
+        <v>1.640446253333333</v>
       </c>
       <c r="Q23">
-        <v>2.099693393333333</v>
+        <v>2.083446253333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1032340265767416</v>
+        <v>0.1037506125326396</v>
       </c>
       <c r="T23">
-        <v>1.051924366750034</v>
+        <v>1.0613858199498</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.855633766146015</v>
+        <v>5.589468594957561</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08883337777545892</v>
+        <v>0.08856342455529197</v>
       </c>
       <c r="C24">
-        <v>32.17113566778577</v>
+        <v>31.91452272062602</v>
       </c>
       <c r="D24">
-        <v>34.46513566778577</v>
+        <v>34.66052272062603</v>
       </c>
       <c r="E24">
-        <v>-12.456</v>
+        <v>-12.004</v>
       </c>
       <c r="F24">
-        <v>9.944000000000001</v>
+        <v>10.396</v>
       </c>
       <c r="G24">
         <v>7.65</v>
@@ -3255,28 +3255,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M24">
-        <v>0.5499032</v>
+        <v>0.5748988</v>
       </c>
       <c r="N24">
-        <v>2.523763466666666</v>
+        <v>2.498767866666666</v>
       </c>
       <c r="O24">
-        <v>0.8833172133333331</v>
+        <v>0.8745687533333332</v>
       </c>
       <c r="P24">
-        <v>1.640446253333333</v>
+        <v>1.624199113333333</v>
       </c>
       <c r="Q24">
-        <v>2.083446253333333</v>
+        <v>2.067199113333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1037506125326396</v>
+        <v>0.104280616305574</v>
       </c>
       <c r="T24">
-        <v>1.0613858199498</v>
+        <v>1.07109302518073</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.589468594957561</v>
+        <v>5.346448221263754</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08856342455529197</v>
+        <v>0.088293471335125</v>
       </c>
       <c r="C25">
-        <v>31.91452272062602</v>
+        <v>31.66013775014896</v>
       </c>
       <c r="D25">
-        <v>34.66052272062603</v>
+        <v>34.85813775014896</v>
       </c>
       <c r="E25">
-        <v>-12.004</v>
+        <v>-11.552</v>
       </c>
       <c r="F25">
-        <v>10.396</v>
+        <v>10.848</v>
       </c>
       <c r="G25">
         <v>7.65</v>
@@ -3337,28 +3337,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M25">
-        <v>0.5748988</v>
+        <v>0.5998944</v>
       </c>
       <c r="N25">
-        <v>2.498767866666666</v>
+        <v>2.473772266666666</v>
       </c>
       <c r="O25">
-        <v>0.8745687533333332</v>
+        <v>0.8658202933333332</v>
       </c>
       <c r="P25">
-        <v>1.624199113333333</v>
+        <v>1.607951973333333</v>
       </c>
       <c r="Q25">
-        <v>2.067199113333333</v>
+        <v>2.050951973333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.104280616305574</v>
+        <v>0.1048245675462171</v>
       </c>
       <c r="T25">
-        <v>1.07109302518073</v>
+        <v>1.081055683180894</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.346448221263754</v>
+        <v>5.123679545377763</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.088293471335125</v>
+        <v>0.08802351811495804</v>
       </c>
       <c r="C26">
-        <v>31.66013775014896</v>
+        <v>31.40801908292426</v>
       </c>
       <c r="D26">
-        <v>34.85813775014896</v>
+        <v>35.05801908292426</v>
       </c>
       <c r="E26">
-        <v>-11.552</v>
+        <v>-11.1</v>
       </c>
       <c r="F26">
-        <v>10.848</v>
+        <v>11.3</v>
       </c>
       <c r="G26">
         <v>7.65</v>
@@ -3419,28 +3419,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M26">
-        <v>0.5998944</v>
+        <v>0.6248900000000001</v>
       </c>
       <c r="N26">
-        <v>2.473772266666666</v>
+        <v>2.448776666666666</v>
       </c>
       <c r="O26">
-        <v>0.8658202933333332</v>
+        <v>0.8570718333333331</v>
       </c>
       <c r="P26">
-        <v>1.607951973333333</v>
+        <v>1.591704833333333</v>
       </c>
       <c r="Q26">
-        <v>2.050951973333333</v>
+        <v>2.034704833333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1048245675462171</v>
+        <v>0.1053830241532774</v>
       </c>
       <c r="T26">
-        <v>1.081055683180894</v>
+        <v>1.091284012061062</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.123679545377763</v>
+        <v>4.918732363562652</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08802351811495804</v>
+        <v>0.08775356489479107</v>
       </c>
       <c r="C27">
-        <v>31.40801908292426</v>
+        <v>31.15820592967066</v>
       </c>
       <c r="D27">
-        <v>35.05801908292426</v>
+        <v>35.26020592967067</v>
       </c>
       <c r="E27">
-        <v>-11.1</v>
+        <v>-10.648</v>
       </c>
       <c r="F27">
-        <v>11.3</v>
+        <v>11.752</v>
       </c>
       <c r="G27">
         <v>7.65</v>
@@ -3501,28 +3501,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M27">
-        <v>0.6248900000000001</v>
+        <v>0.6498856000000001</v>
       </c>
       <c r="N27">
-        <v>2.448776666666666</v>
+        <v>2.423781066666666</v>
       </c>
       <c r="O27">
-        <v>0.8570718333333331</v>
+        <v>0.8483233733333332</v>
       </c>
       <c r="P27">
-        <v>1.591704833333333</v>
+        <v>1.575457693333333</v>
       </c>
       <c r="Q27">
-        <v>2.034704833333333</v>
+        <v>2.018457693333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1053830241532774</v>
+        <v>0.1059565741821501</v>
       </c>
       <c r="T27">
-        <v>1.091284012061062</v>
+        <v>1.101788782262316</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.918732363562652</v>
+        <v>4.729550349579474</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08775356489479107</v>
+        <v>0.08748361167462412</v>
       </c>
       <c r="C28">
-        <v>31.15820592967066</v>
+        <v>30.91073841089912</v>
       </c>
       <c r="D28">
-        <v>35.26020592967067</v>
+        <v>35.46473841089912</v>
       </c>
       <c r="E28">
-        <v>-10.648</v>
+        <v>-10.196</v>
       </c>
       <c r="F28">
-        <v>11.752</v>
+        <v>12.204</v>
       </c>
       <c r="G28">
         <v>7.65</v>
@@ -3583,28 +3583,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M28">
-        <v>0.6498856000000001</v>
+        <v>0.6748812000000002</v>
       </c>
       <c r="N28">
-        <v>2.423781066666666</v>
+        <v>2.398785466666666</v>
       </c>
       <c r="O28">
-        <v>0.8483233733333332</v>
+        <v>0.8395749133333332</v>
       </c>
       <c r="P28">
-        <v>1.575457693333333</v>
+        <v>1.559210553333333</v>
       </c>
       <c r="Q28">
-        <v>2.018457693333333</v>
+        <v>2.002210553333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1059565741821501</v>
+        <v>0.106545837910444</v>
       </c>
       <c r="T28">
-        <v>1.101788782262316</v>
+        <v>1.112581354386893</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.729550349579474</v>
+        <v>4.554381818113567</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08748361167462412</v>
+        <v>0.08766865845445715</v>
       </c>
       <c r="C29">
-        <v>30.91073841089912</v>
+        <v>30.31828127886493</v>
       </c>
       <c r="D29">
-        <v>35.46473841089912</v>
+        <v>35.32428127886493</v>
       </c>
       <c r="E29">
-        <v>-10.196</v>
+        <v>-9.743999999999996</v>
       </c>
       <c r="F29">
-        <v>12.204</v>
+        <v>12.656</v>
       </c>
       <c r="G29">
         <v>7.65</v>
@@ -3665,45 +3665,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M29">
-        <v>0.6748812000000002</v>
+        <v>0.7315168000000002</v>
       </c>
       <c r="N29">
-        <v>2.398785466666666</v>
+        <v>2.342149866666666</v>
       </c>
       <c r="O29">
-        <v>0.8395749133333332</v>
+        <v>0.8197524533333332</v>
       </c>
       <c r="P29">
-        <v>1.559210553333333</v>
+        <v>1.522397413333333</v>
       </c>
       <c r="Q29">
-        <v>2.002210553333333</v>
+        <v>1.965397413333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.106545837910444</v>
+        <v>0.1071514700756349</v>
       </c>
       <c r="T29">
-        <v>1.112581354386893</v>
+        <v>1.123673720181596</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.554381818113567</v>
+        <v>4.2017718071091</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08766865845445715</v>
+        <v>0.08741495523429019</v>
       </c>
       <c r="C30">
-        <v>30.31828127886493</v>
+        <v>30.05913561892889</v>
       </c>
       <c r="D30">
-        <v>35.32428127886493</v>
+        <v>35.5171356189289</v>
       </c>
       <c r="E30">
-        <v>-9.743999999999996</v>
+        <v>-9.291999999999996</v>
       </c>
       <c r="F30">
-        <v>12.656</v>
+        <v>13.108</v>
       </c>
       <c r="G30">
         <v>7.65</v>
@@ -3747,28 +3747,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M30">
-        <v>0.7315168000000002</v>
+        <v>0.7576424000000002</v>
       </c>
       <c r="N30">
-        <v>2.342149866666666</v>
+        <v>2.316024266666666</v>
       </c>
       <c r="O30">
-        <v>0.8197524533333332</v>
+        <v>0.8106084933333331</v>
       </c>
       <c r="P30">
-        <v>1.522397413333333</v>
+        <v>1.505415773333333</v>
       </c>
       <c r="Q30">
-        <v>1.965397413333333</v>
+        <v>1.948415773333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1071514700756349</v>
+        <v>0.1077741623018172</v>
       </c>
       <c r="T30">
-        <v>1.123673720181596</v>
+        <v>1.135078546984601</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.2017718071091</v>
+        <v>4.056883124105338</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08741495523429017</v>
+        <v>0.08784375201412323</v>
       </c>
       <c r="C31">
-        <v>30.0591356189289</v>
+        <v>29.28239957311659</v>
       </c>
       <c r="D31">
-        <v>35.5171356189289</v>
+        <v>35.19239957311659</v>
       </c>
       <c r="E31">
-        <v>-9.291999999999998</v>
+        <v>-8.839999999999998</v>
       </c>
       <c r="F31">
-        <v>13.108</v>
+        <v>13.56</v>
       </c>
       <c r="G31">
         <v>7.65</v>
@@ -3829,45 +3829,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M31">
-        <v>0.7576424</v>
+        <v>0.8312280000000001</v>
       </c>
       <c r="N31">
-        <v>2.316024266666667</v>
+        <v>2.242438666666667</v>
       </c>
       <c r="O31">
-        <v>0.8106084933333333</v>
+        <v>0.7848535333333333</v>
       </c>
       <c r="P31">
-        <v>1.505415773333333</v>
+        <v>1.457585133333333</v>
       </c>
       <c r="Q31">
-        <v>1.948415773333333</v>
+        <v>1.900585133333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1077741623018172</v>
+        <v>0.1084146457344617</v>
       </c>
       <c r="T31">
-        <v>1.135078546984601</v>
+        <v>1.146809225981977</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.056883124105338</v>
+        <v>3.697741975326465</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08784375201412323</v>
+        <v>0.08761279879395625</v>
       </c>
       <c r="C32">
-        <v>29.28239957311659</v>
+        <v>29.00456338932358</v>
       </c>
       <c r="D32">
-        <v>35.19239957311659</v>
+        <v>35.36656338932358</v>
       </c>
       <c r="E32">
-        <v>-8.839999999999998</v>
+        <v>-8.387999999999998</v>
       </c>
       <c r="F32">
-        <v>13.56</v>
+        <v>14.012</v>
       </c>
       <c r="G32">
         <v>7.65</v>
@@ -3911,28 +3911,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M32">
-        <v>0.8312280000000001</v>
+        <v>0.8589356</v>
       </c>
       <c r="N32">
-        <v>2.242438666666667</v>
+        <v>2.214731066666666</v>
       </c>
       <c r="O32">
-        <v>0.7848535333333333</v>
+        <v>0.7751558733333332</v>
       </c>
       <c r="P32">
-        <v>1.457585133333333</v>
+        <v>1.439575193333333</v>
       </c>
       <c r="Q32">
-        <v>1.900585133333333</v>
+        <v>1.882575193333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1084146457344617</v>
+        <v>0.1090736939042844</v>
       </c>
       <c r="T32">
-        <v>1.146809225981977</v>
+        <v>1.158879924660437</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.697741975326465</v>
+        <v>3.578459976122385</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08761279879395625</v>
+        <v>0.0879642455737893</v>
       </c>
       <c r="C33">
-        <v>29.00456338932358</v>
+        <v>28.28821351863076</v>
       </c>
       <c r="D33">
-        <v>35.36656338932358</v>
+        <v>35.10221351863076</v>
       </c>
       <c r="E33">
-        <v>-8.387999999999998</v>
+        <v>-7.935999999999998</v>
       </c>
       <c r="F33">
-        <v>14.012</v>
+        <v>14.464</v>
       </c>
       <c r="G33">
         <v>7.65</v>
@@ -3993,45 +3993,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M33">
-        <v>0.8589356</v>
+        <v>0.9271424</v>
       </c>
       <c r="N33">
-        <v>2.214731066666666</v>
+        <v>2.146524266666666</v>
       </c>
       <c r="O33">
-        <v>0.7751558733333332</v>
+        <v>0.7512834933333332</v>
       </c>
       <c r="P33">
-        <v>1.439575193333333</v>
+        <v>1.395240773333333</v>
       </c>
       <c r="Q33">
-        <v>1.882575193333333</v>
+        <v>1.838240773333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1090736939042844</v>
+        <v>0.1097521258438078</v>
       </c>
       <c r="T33">
-        <v>1.158879924660437</v>
+        <v>1.171305643888263</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.578459976122385</v>
+        <v>3.3152045108353</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0879642455737893</v>
+        <v>0.08775149235362234</v>
       </c>
       <c r="C34">
-        <v>28.28821351863076</v>
+        <v>27.99576722210039</v>
       </c>
       <c r="D34">
-        <v>35.10221351863076</v>
+        <v>35.2617672221004</v>
       </c>
       <c r="E34">
-        <v>-7.935999999999998</v>
+        <v>-7.483999999999996</v>
       </c>
       <c r="F34">
-        <v>14.464</v>
+        <v>14.916</v>
       </c>
       <c r="G34">
         <v>7.65</v>
@@ -4075,28 +4075,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M34">
-        <v>0.9271424</v>
+        <v>0.9561156000000002</v>
       </c>
       <c r="N34">
-        <v>2.146524266666666</v>
+        <v>2.117551066666667</v>
       </c>
       <c r="O34">
-        <v>0.7512834933333332</v>
+        <v>0.7411428733333333</v>
       </c>
       <c r="P34">
-        <v>1.395240773333333</v>
+        <v>1.376408193333333</v>
       </c>
       <c r="Q34">
-        <v>1.838240773333333</v>
+        <v>1.819408193333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1097521258438078</v>
+        <v>0.1104508094830184</v>
       </c>
       <c r="T34">
-        <v>1.171305643888263</v>
+        <v>1.184102280107965</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.3152045108353</v>
+        <v>3.214743768082715</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08775149235362234</v>
+        <v>0.08753873913345538</v>
       </c>
       <c r="C35">
-        <v>27.99576722210039</v>
+        <v>27.70477802038911</v>
       </c>
       <c r="D35">
-        <v>35.2617672221004</v>
+        <v>35.42277802038912</v>
       </c>
       <c r="E35">
-        <v>-7.483999999999996</v>
+        <v>-7.031999999999996</v>
       </c>
       <c r="F35">
-        <v>14.916</v>
+        <v>15.368</v>
       </c>
       <c r="G35">
         <v>7.65</v>
@@ -4157,28 +4157,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M35">
-        <v>0.9561156000000002</v>
+        <v>0.9850888000000002</v>
       </c>
       <c r="N35">
-        <v>2.117551066666667</v>
+        <v>2.088577866666666</v>
       </c>
       <c r="O35">
-        <v>0.7411428733333333</v>
+        <v>0.7310022533333331</v>
       </c>
       <c r="P35">
-        <v>1.376408193333333</v>
+        <v>1.357575613333333</v>
       </c>
       <c r="Q35">
-        <v>1.819408193333333</v>
+        <v>1.800575613333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1104508094830184</v>
+        <v>0.1111706653537203</v>
       </c>
       <c r="T35">
-        <v>1.184102280107965</v>
+        <v>1.197286693182809</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.214743768082715</v>
+        <v>3.120192480786165</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08753873913345538</v>
+        <v>0.08732598591328841</v>
       </c>
       <c r="C36">
-        <v>27.70477802038911</v>
+        <v>27.41526596503061</v>
       </c>
       <c r="D36">
-        <v>35.42277802038912</v>
+        <v>35.58526596503062</v>
       </c>
       <c r="E36">
-        <v>-7.031999999999996</v>
+        <v>-6.579999999999997</v>
       </c>
       <c r="F36">
-        <v>15.368</v>
+        <v>15.82</v>
       </c>
       <c r="G36">
         <v>7.65</v>
@@ -4239,28 +4239,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M36">
-        <v>0.9850888000000002</v>
+        <v>1.014062</v>
       </c>
       <c r="N36">
-        <v>2.088577866666666</v>
+        <v>2.059604666666666</v>
       </c>
       <c r="O36">
-        <v>0.7310022533333331</v>
+        <v>0.7208616333333331</v>
       </c>
       <c r="P36">
-        <v>1.357575613333333</v>
+        <v>1.338743033333333</v>
       </c>
       <c r="Q36">
-        <v>1.800575613333333</v>
+        <v>1.781743033333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1111706653537203</v>
+        <v>0.1119126706358283</v>
       </c>
       <c r="T36">
-        <v>1.197286693182809</v>
+        <v>1.21087678050611</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.120192480786165</v>
+        <v>3.031044124192274</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08732598591328841</v>
+        <v>0.08893843269312145</v>
       </c>
       <c r="C37">
-        <v>27.41526596503061</v>
+        <v>25.76769303295639</v>
       </c>
       <c r="D37">
-        <v>35.58526596503062</v>
+        <v>34.38969303295639</v>
       </c>
       <c r="E37">
-        <v>-6.579999999999997</v>
+        <v>-6.127999999999997</v>
       </c>
       <c r="F37">
-        <v>15.82</v>
+        <v>16.272</v>
       </c>
       <c r="G37">
         <v>7.65</v>
@@ -4321,45 +4321,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M37">
-        <v>1.014062</v>
+        <v>1.1699568</v>
       </c>
       <c r="N37">
-        <v>2.059604666666666</v>
+        <v>1.903709866666666</v>
       </c>
       <c r="O37">
-        <v>0.7208616333333331</v>
+        <v>0.6662984533333332</v>
       </c>
       <c r="P37">
-        <v>1.338743033333333</v>
+        <v>1.237411413333333</v>
       </c>
       <c r="Q37">
-        <v>1.781743033333333</v>
+        <v>1.680411413333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1119126706358283</v>
+        <v>0.1126778635830023</v>
       </c>
       <c r="T37">
-        <v>1.21087678050611</v>
+        <v>1.224891558058264</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.031044124192274</v>
+        <v>2.627162529989711</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08893843269312146</v>
+        <v>0.08877637947295448</v>
       </c>
       <c r="C38">
-        <v>25.76769303295638</v>
+        <v>25.43220629147558</v>
       </c>
       <c r="D38">
-        <v>34.38969303295639</v>
+        <v>34.50620629147558</v>
       </c>
       <c r="E38">
-        <v>-6.127999999999997</v>
+        <v>-5.675999999999998</v>
       </c>
       <c r="F38">
-        <v>16.272</v>
+        <v>16.724</v>
       </c>
       <c r="G38">
         <v>7.65</v>
@@ -4403,28 +4403,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M38">
-        <v>1.1699568</v>
+        <v>1.2024556</v>
       </c>
       <c r="N38">
-        <v>1.903709866666666</v>
+        <v>1.871211066666666</v>
       </c>
       <c r="O38">
-        <v>0.6662984533333332</v>
+        <v>0.6549238733333332</v>
       </c>
       <c r="P38">
-        <v>1.237411413333333</v>
+        <v>1.216287193333333</v>
       </c>
       <c r="Q38">
-        <v>1.680411413333333</v>
+        <v>1.659287193333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1126778635830023</v>
+        <v>0.113467348369769</v>
       </c>
       <c r="T38">
-        <v>1.224891558058264</v>
+        <v>1.239351249183502</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.627162529989711</v>
+        <v>2.556158137287286</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08877637947295448</v>
+        <v>0.08957762625278752</v>
       </c>
       <c r="C39">
-        <v>25.43220629147558</v>
+        <v>24.41169637977404</v>
       </c>
       <c r="D39">
-        <v>34.50620629147558</v>
+        <v>33.93769637977404</v>
       </c>
       <c r="E39">
-        <v>-5.675999999999998</v>
+        <v>-5.223999999999997</v>
       </c>
       <c r="F39">
-        <v>16.724</v>
+        <v>17.176</v>
       </c>
       <c r="G39">
         <v>7.65</v>
@@ -4485,45 +4485,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M39">
-        <v>1.2024556</v>
+        <v>1.3019408</v>
       </c>
       <c r="N39">
-        <v>1.871211066666666</v>
+        <v>1.771725866666666</v>
       </c>
       <c r="O39">
-        <v>0.6549238733333332</v>
+        <v>0.6201040533333332</v>
       </c>
       <c r="P39">
-        <v>1.216287193333333</v>
+        <v>1.151621813333333</v>
       </c>
       <c r="Q39">
-        <v>1.659287193333333</v>
+        <v>1.594621813333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.113467348369769</v>
+        <v>0.1142823004077218</v>
       </c>
       <c r="T39">
-        <v>1.239351249183502</v>
+        <v>1.254277381957942</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.556158137287286</v>
+        <v>2.360834430157397</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08957762625278752</v>
+        <v>0.08944092303262058</v>
       </c>
       <c r="C40">
-        <v>24.41169637977404</v>
+        <v>24.0553624939047</v>
       </c>
       <c r="D40">
-        <v>33.93769637977404</v>
+        <v>34.0333624939047</v>
       </c>
       <c r="E40">
-        <v>-5.223999999999997</v>
+        <v>-4.771999999999998</v>
       </c>
       <c r="F40">
-        <v>17.176</v>
+        <v>17.628</v>
       </c>
       <c r="G40">
         <v>7.65</v>
@@ -4567,28 +4567,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M40">
-        <v>1.3019408</v>
+        <v>1.3362024</v>
       </c>
       <c r="N40">
-        <v>1.771725866666666</v>
+        <v>1.737464266666666</v>
       </c>
       <c r="O40">
-        <v>0.6201040533333332</v>
+        <v>0.6081124933333332</v>
       </c>
       <c r="P40">
-        <v>1.151621813333333</v>
+        <v>1.129351773333333</v>
       </c>
       <c r="Q40">
-        <v>1.594621813333333</v>
+        <v>1.572351773333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1142823004077218</v>
+        <v>0.1151239721846239</v>
       </c>
       <c r="T40">
-        <v>1.254277381957942</v>
+        <v>1.269692896134822</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.360834430157397</v>
+        <v>2.300300213999515</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08944092303262058</v>
+        <v>0.08930421981245361</v>
       </c>
       <c r="C41">
-        <v>24.0553624939047</v>
+        <v>23.69956947424943</v>
       </c>
       <c r="D41">
-        <v>34.0333624939047</v>
+        <v>34.12956947424943</v>
       </c>
       <c r="E41">
-        <v>-4.771999999999998</v>
+        <v>-4.319999999999997</v>
       </c>
       <c r="F41">
-        <v>17.628</v>
+        <v>18.08</v>
       </c>
       <c r="G41">
         <v>7.65</v>
@@ -4649,28 +4649,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M41">
-        <v>1.3362024</v>
+        <v>1.370464</v>
       </c>
       <c r="N41">
-        <v>1.737464266666666</v>
+        <v>1.703202666666666</v>
       </c>
       <c r="O41">
-        <v>0.6081124933333332</v>
+        <v>0.5961209333333332</v>
       </c>
       <c r="P41">
-        <v>1.129351773333333</v>
+        <v>1.107081733333333</v>
       </c>
       <c r="Q41">
-        <v>1.572351773333333</v>
+        <v>1.550081733333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1151239721846239</v>
+        <v>0.1159936996874227</v>
       </c>
       <c r="T41">
-        <v>1.269692896134822</v>
+        <v>1.285622260784265</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.300300213999515</v>
+        <v>2.242792708649527</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08930421981245361</v>
+        <v>0.08916751659228664</v>
       </c>
       <c r="C42">
-        <v>23.69956947424943</v>
+        <v>23.34432192064321</v>
       </c>
       <c r="D42">
-        <v>34.12956947424943</v>
+        <v>34.22632192064322</v>
       </c>
       <c r="E42">
-        <v>-4.319999999999997</v>
+        <v>-3.867999999999995</v>
       </c>
       <c r="F42">
-        <v>18.08</v>
+        <v>18.532</v>
       </c>
       <c r="G42">
         <v>7.65</v>
@@ -4731,28 +4731,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M42">
-        <v>1.370464</v>
+        <v>1.4047256</v>
       </c>
       <c r="N42">
-        <v>1.703202666666666</v>
+        <v>1.668941066666666</v>
       </c>
       <c r="O42">
-        <v>0.5961209333333332</v>
+        <v>0.5841293733333331</v>
       </c>
       <c r="P42">
-        <v>1.107081733333333</v>
+        <v>1.084811693333333</v>
       </c>
       <c r="Q42">
-        <v>1.550081733333333</v>
+        <v>1.527811693333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1159936996874227</v>
+        <v>0.1168929094784519</v>
       </c>
       <c r="T42">
-        <v>1.285622260784265</v>
+        <v>1.302091603896401</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.242792708649527</v>
+        <v>2.188090447462954</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08916751659228664</v>
+        <v>0.08903081337211967</v>
       </c>
       <c r="C43">
-        <v>23.34432192064321</v>
+        <v>22.98962448522883</v>
       </c>
       <c r="D43">
-        <v>34.22632192064322</v>
+        <v>34.32362448522883</v>
       </c>
       <c r="E43">
-        <v>-3.867999999999995</v>
+        <v>-3.415999999999997</v>
       </c>
       <c r="F43">
-        <v>18.532</v>
+        <v>18.984</v>
       </c>
       <c r="G43">
         <v>7.65</v>
@@ -4813,28 +4813,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M43">
-        <v>1.4047256</v>
+        <v>1.4389872</v>
       </c>
       <c r="N43">
-        <v>1.668941066666666</v>
+        <v>1.634679466666666</v>
       </c>
       <c r="O43">
-        <v>0.5841293733333331</v>
+        <v>0.5721378133333331</v>
       </c>
       <c r="P43">
-        <v>1.084811693333333</v>
+        <v>1.062541653333333</v>
       </c>
       <c r="Q43">
-        <v>1.527811693333333</v>
+        <v>1.505541653333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1168929094784519</v>
+        <v>0.1178231265036546</v>
       </c>
       <c r="T43">
-        <v>1.302091603896401</v>
+        <v>1.319128855391714</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.188090447462954</v>
+        <v>2.135993055856693</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08903081337211968</v>
+        <v>0.08889411015195273</v>
       </c>
       <c r="C44">
-        <v>22.98962448522882</v>
+        <v>22.63548187320248</v>
       </c>
       <c r="D44">
-        <v>34.32362448522882</v>
+        <v>34.42148187320248</v>
       </c>
       <c r="E44">
-        <v>-3.415999999999997</v>
+        <v>-2.963999999999999</v>
       </c>
       <c r="F44">
-        <v>18.984</v>
+        <v>19.436</v>
       </c>
       <c r="G44">
         <v>7.65</v>
@@ -4895,28 +4895,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M44">
-        <v>1.4389872</v>
+        <v>1.4732488</v>
       </c>
       <c r="N44">
-        <v>1.634679466666666</v>
+        <v>1.600417866666666</v>
       </c>
       <c r="O44">
-        <v>0.5721378133333331</v>
+        <v>0.5601462533333332</v>
       </c>
       <c r="P44">
-        <v>1.062541653333333</v>
+        <v>1.040271613333333</v>
       </c>
       <c r="Q44">
-        <v>1.505541653333333</v>
+        <v>1.483271613333333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1178231265036546</v>
+        <v>0.1187859827227241</v>
       </c>
       <c r="T44">
-        <v>1.319128855391714</v>
+        <v>1.336763905185108</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.135993055856693</v>
+        <v>2.086318798743747</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08889411015195273</v>
+        <v>0.08875740693178577</v>
       </c>
       <c r="C45">
-        <v>22.63548187320248</v>
+        <v>22.28189884357227</v>
       </c>
       <c r="D45">
-        <v>34.42148187320248</v>
+        <v>34.51989884357227</v>
       </c>
       <c r="E45">
-        <v>-2.963999999999999</v>
+        <v>-2.511999999999997</v>
       </c>
       <c r="F45">
-        <v>19.436</v>
+        <v>19.888</v>
       </c>
       <c r="G45">
         <v>7.65</v>
@@ -4977,28 +4977,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M45">
-        <v>1.4732488</v>
+        <v>1.5075104</v>
       </c>
       <c r="N45">
-        <v>1.600417866666666</v>
+        <v>1.566156266666666</v>
       </c>
       <c r="O45">
-        <v>0.5601462533333332</v>
+        <v>0.5481546933333331</v>
       </c>
       <c r="P45">
-        <v>1.040271613333333</v>
+        <v>1.018001573333333</v>
       </c>
       <c r="Q45">
-        <v>1.483271613333333</v>
+        <v>1.461001573333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1187859827227241</v>
+        <v>0.1197832266639031</v>
       </c>
       <c r="T45">
-        <v>1.336763905185108</v>
+        <v>1.355028778185409</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.086318798743747</v>
+        <v>2.038902462408661</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08875740693178577</v>
+        <v>0.09277420371161879</v>
       </c>
       <c r="C46">
-        <v>22.28189884357227</v>
+        <v>19.15457135794086</v>
       </c>
       <c r="D46">
-        <v>34.51989884357227</v>
+        <v>31.84457135794086</v>
       </c>
       <c r="E46">
-        <v>-2.511999999999997</v>
+        <v>-2.059999999999995</v>
       </c>
       <c r="F46">
-        <v>19.888</v>
+        <v>20.34</v>
       </c>
       <c r="G46">
         <v>7.65</v>
@@ -5059,45 +5059,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M46">
-        <v>1.5075104</v>
+        <v>1.8306</v>
       </c>
       <c r="N46">
-        <v>1.566156266666666</v>
+        <v>1.243066666666666</v>
       </c>
       <c r="O46">
-        <v>0.5481546933333331</v>
+        <v>0.4350733333333332</v>
       </c>
       <c r="P46">
-        <v>1.018001573333333</v>
+        <v>0.8079933333333331</v>
       </c>
       <c r="Q46">
-        <v>1.461001573333333</v>
+        <v>1.250993333333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1197832266639031</v>
+        <v>0.1208167340211251</v>
       </c>
       <c r="T46">
-        <v>1.355028778185409</v>
+        <v>1.373957828385721</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.35</v>
       </c>
       <c r="W46">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.038902462408661</v>
+        <v>1.679048763611202</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09277420371161879</v>
+        <v>0.09272980049145184</v>
       </c>
       <c r="C47">
-        <v>19.15457135794086</v>
+        <v>18.72987682955237</v>
       </c>
       <c r="D47">
-        <v>31.84457135794086</v>
+        <v>31.87187682955237</v>
       </c>
       <c r="E47">
-        <v>-2.059999999999995</v>
+        <v>-1.607999999999997</v>
       </c>
       <c r="F47">
-        <v>20.34</v>
+        <v>20.792</v>
       </c>
       <c r="G47">
         <v>7.65</v>
@@ -5141,28 +5141,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M47">
-        <v>1.8306</v>
+        <v>1.87128</v>
       </c>
       <c r="N47">
-        <v>1.243066666666666</v>
+        <v>1.202386666666666</v>
       </c>
       <c r="O47">
-        <v>0.4350733333333332</v>
+        <v>0.4208353333333332</v>
       </c>
       <c r="P47">
-        <v>0.8079933333333331</v>
+        <v>0.7815513333333333</v>
       </c>
       <c r="Q47">
-        <v>1.250993333333333</v>
+        <v>1.224551333333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1208167340211251</v>
+        <v>0.1218885194286145</v>
       </c>
       <c r="T47">
-        <v>1.373957828385721</v>
+        <v>1.393587954519378</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.679048763611202</v>
+        <v>1.642547703532698</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09272980049145184</v>
+        <v>0.09268539727128489</v>
       </c>
       <c r="C48">
-        <v>18.72987682955237</v>
+        <v>18.30522916809345</v>
       </c>
       <c r="D48">
-        <v>31.87187682955237</v>
+        <v>31.89922916809346</v>
       </c>
       <c r="E48">
-        <v>-1.607999999999997</v>
+        <v>-1.155999999999995</v>
       </c>
       <c r="F48">
-        <v>20.792</v>
+        <v>21.244</v>
       </c>
       <c r="G48">
         <v>7.65</v>
@@ -5223,28 +5223,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M48">
-        <v>1.87128</v>
+        <v>1.91196</v>
       </c>
       <c r="N48">
-        <v>1.202386666666666</v>
+        <v>1.161706666666666</v>
       </c>
       <c r="O48">
-        <v>0.4208353333333332</v>
+        <v>0.4065973333333331</v>
       </c>
       <c r="P48">
-        <v>0.7815513333333333</v>
+        <v>0.7551093333333331</v>
       </c>
       <c r="Q48">
-        <v>1.224551333333333</v>
+        <v>1.198109333333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1218885194286145</v>
+        <v>0.123000749568462</v>
       </c>
       <c r="T48">
-        <v>1.393587954519378</v>
+        <v>1.413958840129776</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.642547703532698</v>
+        <v>1.607599880053278</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09268539727128489</v>
+        <v>0.09264099405111792</v>
       </c>
       <c r="C49">
-        <v>18.30522916809345</v>
+        <v>17.8806284943309</v>
       </c>
       <c r="D49">
-        <v>31.89922916809346</v>
+        <v>31.92662849433091</v>
       </c>
       <c r="E49">
-        <v>-1.155999999999995</v>
+        <v>-0.7039999999999971</v>
       </c>
       <c r="F49">
-        <v>21.244</v>
+        <v>21.696</v>
       </c>
       <c r="G49">
         <v>7.65</v>
@@ -5305,28 +5305,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M49">
-        <v>1.91196</v>
+        <v>1.95264</v>
       </c>
       <c r="N49">
-        <v>1.161706666666666</v>
+        <v>1.121026666666666</v>
       </c>
       <c r="O49">
-        <v>0.4065973333333331</v>
+        <v>0.3923593333333332</v>
       </c>
       <c r="P49">
-        <v>0.7551093333333331</v>
+        <v>0.7286673333333331</v>
       </c>
       <c r="Q49">
-        <v>1.198109333333333</v>
+        <v>1.171667333333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.123000749568462</v>
+        <v>0.1241557577906114</v>
       </c>
       <c r="T49">
-        <v>1.413958840129776</v>
+        <v>1.435113221340575</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.607599880053278</v>
+        <v>1.574108215885502</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09264099405111791</v>
+        <v>0.09259659083095094</v>
       </c>
       <c r="C50">
-        <v>17.88062849433091</v>
+        <v>17.45607492944677</v>
       </c>
       <c r="D50">
-        <v>31.92662849433091</v>
+        <v>31.95407492944677</v>
       </c>
       <c r="E50">
-        <v>-0.7039999999999971</v>
+        <v>-0.2519999999999989</v>
       </c>
       <c r="F50">
-        <v>21.696</v>
+        <v>22.148</v>
       </c>
       <c r="G50">
         <v>7.65</v>
@@ -5387,28 +5387,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M50">
-        <v>1.95264</v>
+        <v>1.99332</v>
       </c>
       <c r="N50">
-        <v>1.121026666666666</v>
+        <v>1.080346666666667</v>
       </c>
       <c r="O50">
-        <v>0.3923593333333332</v>
+        <v>0.3781213333333333</v>
       </c>
       <c r="P50">
-        <v>0.7286673333333331</v>
+        <v>0.7022253333333333</v>
       </c>
       <c r="Q50">
-        <v>1.171667333333333</v>
+        <v>1.145225333333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1241557577906114</v>
+        <v>0.125356060452845</v>
       </c>
       <c r="T50">
-        <v>1.435113221340575</v>
+        <v>1.457097186128268</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.574108215885502</v>
+        <v>1.541983558418451</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09259659083095094</v>
+        <v>0.09255218761078397</v>
       </c>
       <c r="C51">
-        <v>17.45607492944677</v>
+        <v>17.03156859504014</v>
       </c>
       <c r="D51">
-        <v>31.95407492944677</v>
+        <v>31.98156859504014</v>
       </c>
       <c r="E51">
-        <v>-0.2519999999999989</v>
+        <v>0.2000000000000028</v>
       </c>
       <c r="F51">
-        <v>22.148</v>
+        <v>22.6</v>
       </c>
       <c r="G51">
         <v>7.65</v>
@@ -5469,28 +5469,28 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M51">
-        <v>1.99332</v>
+        <v>2.034</v>
       </c>
       <c r="N51">
-        <v>1.080346666666667</v>
+        <v>1.039666666666666</v>
       </c>
       <c r="O51">
-        <v>0.3781213333333333</v>
+        <v>0.3638833333333332</v>
       </c>
       <c r="P51">
-        <v>0.7022253333333333</v>
+        <v>0.6757833333333332</v>
       </c>
       <c r="Q51">
-        <v>1.145225333333333</v>
+        <v>1.118783333333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.125356060452845</v>
+        <v>0.1266043752215679</v>
       </c>
       <c r="T51">
-        <v>1.457097186128268</v>
+        <v>1.479960509507468</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.541983558418451</v>
+        <v>1.511143887250082</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09255218761078397</v>
+        <v>0.1145420014831839</v>
       </c>
       <c r="C52">
-        <v>17.03156859504014</v>
+        <v>7.023864740491444</v>
       </c>
       <c r="D52">
-        <v>31.98156859504014</v>
+        <v>22.42586474049145</v>
       </c>
       <c r="E52">
-        <v>0.2000000000000028</v>
+        <v>0.6520000000000046</v>
       </c>
       <c r="F52">
-        <v>22.6</v>
+        <v>23.052</v>
       </c>
       <c r="G52">
         <v>7.65</v>
@@ -5551,45 +5551,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M52">
-        <v>2.034</v>
+        <v>3.384033600000001</v>
       </c>
       <c r="N52">
-        <v>1.039666666666666</v>
+        <v>-0.3103669333333343</v>
       </c>
       <c r="O52">
-        <v>0.3638833333333332</v>
+        <v>-0.108628426666667</v>
       </c>
       <c r="P52">
-        <v>0.6757833333333332</v>
+        <v>-0.2017385066666673</v>
       </c>
       <c r="Q52">
-        <v>1.118783333333333</v>
+        <v>0.2412614933333327</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1266043752215679</v>
+        <v>0.1295398320558626</v>
       </c>
       <c r="T52">
-        <v>1.479960509507468</v>
+        <v>1.533724432317434</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.35</v>
+        <v>0.3178997198294169</v>
       </c>
       <c r="W52">
-        <v>0.0585</v>
+        <v>0.1001323211290416</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.511143887250082</v>
+        <v>0.908284913798334</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1145420014831839</v>
+        <v>0.1155520014831839</v>
       </c>
       <c r="C53">
-        <v>7.023864740491444</v>
+        <v>6.268271250528773</v>
       </c>
       <c r="D53">
-        <v>22.42586474049145</v>
+        <v>22.12227125052878</v>
       </c>
       <c r="E53">
-        <v>0.6520000000000046</v>
+        <v>1.104000000000003</v>
       </c>
       <c r="F53">
-        <v>23.052</v>
+        <v>23.504</v>
       </c>
       <c r="G53">
         <v>7.65</v>
@@ -5633,37 +5633,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M53">
-        <v>3.384033600000001</v>
+        <v>3.450387200000001</v>
       </c>
       <c r="N53">
-        <v>-0.3103669333333343</v>
+        <v>-0.3767205333333341</v>
       </c>
       <c r="O53">
-        <v>-0.108628426666667</v>
+        <v>-0.1318521866666669</v>
       </c>
       <c r="P53">
-        <v>-0.2017385066666673</v>
+        <v>-0.2448683466666672</v>
       </c>
       <c r="Q53">
-        <v>0.2412614933333327</v>
+        <v>0.1981316533333328</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1295398320558626</v>
+        <v>0.1312844118903597</v>
       </c>
       <c r="T53">
-        <v>1.533724432317434</v>
+        <v>1.56567702465738</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.3178997198294169</v>
+        <v>0.3117862636788512</v>
       </c>
       <c r="W53">
-        <v>0.1001323211290416</v>
+        <v>0.1010297764919447</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.908284913798334</v>
+        <v>0.8908178962252892</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1155520014831839</v>
+        <v>0.1165620014831839</v>
       </c>
       <c r="C54">
-        <v>6.268271250528773</v>
+        <v>5.520787853311234</v>
       </c>
       <c r="D54">
-        <v>22.12227125052878</v>
+        <v>21.82678785331123</v>
       </c>
       <c r="E54">
-        <v>1.104000000000003</v>
+        <v>1.556000000000004</v>
       </c>
       <c r="F54">
-        <v>23.504</v>
+        <v>23.956</v>
       </c>
       <c r="G54">
         <v>7.65</v>
@@ -5715,37 +5715,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M54">
-        <v>3.450387200000001</v>
+        <v>3.516740800000001</v>
       </c>
       <c r="N54">
-        <v>-0.3767205333333341</v>
+        <v>-0.4430741333333343</v>
       </c>
       <c r="O54">
-        <v>-0.1318521866666669</v>
+        <v>-0.155075946666667</v>
       </c>
       <c r="P54">
-        <v>-0.2448683466666672</v>
+        <v>-0.2879981866666673</v>
       </c>
       <c r="Q54">
-        <v>0.1981316533333328</v>
+        <v>0.1550018133333327</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1312844118903597</v>
+        <v>0.1331032291646227</v>
       </c>
       <c r="T54">
-        <v>1.56567702465738</v>
+        <v>1.59898930177775</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.3117862636788512</v>
+        <v>0.3059035039867974</v>
       </c>
       <c r="W54">
-        <v>0.1010297764919447</v>
+        <v>0.1018933656147381</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8908178962252892</v>
+        <v>0.8740100113908497</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1165620014831839</v>
+        <v>0.1175720014831839</v>
       </c>
       <c r="C55">
-        <v>5.520787853311234</v>
+        <v>4.781093856897034</v>
       </c>
       <c r="D55">
-        <v>21.82678785331123</v>
+        <v>21.53909385689704</v>
       </c>
       <c r="E55">
-        <v>1.556000000000004</v>
+        <v>2.008000000000006</v>
       </c>
       <c r="F55">
-        <v>23.956</v>
+        <v>24.408</v>
       </c>
       <c r="G55">
         <v>7.65</v>
@@ -5797,37 +5797,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M55">
-        <v>3.516740800000001</v>
+        <v>3.583094400000001</v>
       </c>
       <c r="N55">
-        <v>-0.4430741333333343</v>
+        <v>-0.5094277333333346</v>
       </c>
       <c r="O55">
-        <v>-0.155075946666667</v>
+        <v>-0.1782997066666671</v>
       </c>
       <c r="P55">
-        <v>-0.2879981866666673</v>
+        <v>-0.3311280266666675</v>
       </c>
       <c r="Q55">
-        <v>0.1550018133333327</v>
+        <v>0.1118719733333325</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1331032291646227</v>
+        <v>0.1350011254508102</v>
       </c>
       <c r="T55">
-        <v>1.59898930177775</v>
+        <v>1.633749938772919</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.3059035039867974</v>
+        <v>0.3002386242833381</v>
       </c>
       <c r="W55">
-        <v>0.1018933656147381</v>
+        <v>0.102724969955206</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8740100113908497</v>
+        <v>0.8578246408095376</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1175720014831839</v>
+        <v>0.1185820014831839</v>
       </c>
       <c r="C56">
-        <v>4.781093856897034</v>
+        <v>4.048885257259055</v>
       </c>
       <c r="D56">
-        <v>21.53909385689704</v>
+        <v>21.25888525725906</v>
       </c>
       <c r="E56">
-        <v>2.008000000000006</v>
+        <v>2.460000000000004</v>
       </c>
       <c r="F56">
-        <v>24.408</v>
+        <v>24.86</v>
       </c>
       <c r="G56">
         <v>7.65</v>
@@ -5879,37 +5879,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M56">
-        <v>3.583094400000001</v>
+        <v>3.649448000000001</v>
       </c>
       <c r="N56">
-        <v>-0.5094277333333346</v>
+        <v>-0.5757813333333344</v>
       </c>
       <c r="O56">
-        <v>-0.1782997066666671</v>
+        <v>-0.201523466666667</v>
       </c>
       <c r="P56">
-        <v>-0.3311280266666675</v>
+        <v>-0.3742578666666674</v>
       </c>
       <c r="Q56">
-        <v>0.1118719733333325</v>
+        <v>0.06874213333333262</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1350011254508102</v>
+        <v>0.1369833726830504</v>
       </c>
       <c r="T56">
-        <v>1.633749938772919</v>
+        <v>1.670055492967872</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.3002386242833381</v>
+        <v>0.2947797402054593</v>
       </c>
       <c r="W56">
-        <v>0.102724969955206</v>
+        <v>0.1035263341378386</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8578246408095376</v>
+        <v>0.8422278291584552</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1185820014831839</v>
+        <v>0.1195920014831839</v>
       </c>
       <c r="C57">
-        <v>4.048885257259055</v>
+        <v>3.323873666734215</v>
       </c>
       <c r="D57">
-        <v>21.25888525725906</v>
+        <v>20.98587366673422</v>
       </c>
       <c r="E57">
-        <v>2.460000000000004</v>
+        <v>2.912000000000006</v>
       </c>
       <c r="F57">
-        <v>24.86</v>
+        <v>25.312</v>
       </c>
       <c r="G57">
         <v>7.65</v>
@@ -5961,37 +5961,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M57">
-        <v>3.649448000000001</v>
+        <v>3.715801600000001</v>
       </c>
       <c r="N57">
-        <v>-0.5757813333333344</v>
+        <v>-0.6421349333333346</v>
       </c>
       <c r="O57">
-        <v>-0.201523466666667</v>
+        <v>-0.2247472266666671</v>
       </c>
       <c r="P57">
-        <v>-0.3742578666666674</v>
+        <v>-0.4173877066666675</v>
       </c>
       <c r="Q57">
-        <v>0.06874213333333262</v>
+        <v>0.02561229333333254</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1369833726830504</v>
+        <v>0.1390557220622106</v>
       </c>
       <c r="T57">
-        <v>1.670055492967872</v>
+        <v>1.708011299626233</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2947797402054593</v>
+        <v>0.2895158162732189</v>
       </c>
       <c r="W57">
-        <v>0.1035263341378386</v>
+        <v>0.1042990781710915</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8422278291584552</v>
+        <v>0.8271880464949113</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1195920014831839</v>
+        <v>0.1206020014831839</v>
       </c>
       <c r="C58">
-        <v>3.323873666734215</v>
+        <v>2.605785323992684</v>
       </c>
       <c r="D58">
-        <v>20.98587366673422</v>
+        <v>20.71978532399269</v>
       </c>
       <c r="E58">
-        <v>2.912000000000006</v>
+        <v>3.364000000000004</v>
       </c>
       <c r="F58">
-        <v>25.312</v>
+        <v>25.764</v>
       </c>
       <c r="G58">
         <v>7.65</v>
@@ -6043,37 +6043,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M58">
-        <v>3.715801600000001</v>
+        <v>3.782155200000001</v>
       </c>
       <c r="N58">
-        <v>-0.6421349333333346</v>
+        <v>-0.7084885333333344</v>
       </c>
       <c r="O58">
-        <v>-0.2247472266666671</v>
+        <v>-0.247970986666667</v>
       </c>
       <c r="P58">
-        <v>-0.4173877066666675</v>
+        <v>-0.4605175466666673</v>
       </c>
       <c r="Q58">
-        <v>0.02561229333333254</v>
+        <v>-0.01751754666666733</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1390557220622106</v>
+        <v>0.1412244597845876</v>
       </c>
       <c r="T58">
-        <v>1.708011299626233</v>
+        <v>1.747732492640797</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2895158162732189</v>
+        <v>0.2844365914263203</v>
       </c>
       <c r="W58">
-        <v>0.1042990781710915</v>
+        <v>0.1050447083786162</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8271880464949113</v>
+        <v>0.8126759755037725</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1206020014831839</v>
+        <v>0.1550672149753901</v>
       </c>
       <c r="C59">
-        <v>2.605785323992684</v>
+        <v>-4.103658969580792</v>
       </c>
       <c r="D59">
-        <v>20.71978532399269</v>
+        <v>14.46234103041921</v>
       </c>
       <c r="E59">
-        <v>3.364000000000004</v>
+        <v>3.816000000000006</v>
       </c>
       <c r="F59">
-        <v>25.764</v>
+        <v>26.216</v>
       </c>
       <c r="G59">
         <v>7.65</v>
@@ -6125,45 +6125,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M59">
-        <v>3.782155200000001</v>
+        <v>5.264172800000001</v>
       </c>
       <c r="N59">
-        <v>-0.7084885333333344</v>
+        <v>-2.190506133333334</v>
       </c>
       <c r="O59">
-        <v>-0.247970986666667</v>
+        <v>-0.766677146666667</v>
       </c>
       <c r="P59">
-        <v>-0.4605175466666673</v>
+        <v>-1.423828986666667</v>
       </c>
       <c r="Q59">
-        <v>-0.01751754666666733</v>
+        <v>-0.9808289866666673</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1412244597845876</v>
+        <v>0.1485803123799498</v>
       </c>
       <c r="T59">
-        <v>1.747732492640797</v>
+        <v>1.882457516193583</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.2844365914263203</v>
+        <v>0.2043594262964417</v>
       </c>
       <c r="W59">
-        <v>0.1050447083786162</v>
+        <v>0.1597646271996745</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8126759755037725</v>
+        <v>0.5838840751326906</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1550672149753901</v>
+        <v>0.1566172149753901</v>
       </c>
       <c r="C60">
-        <v>-4.103658969580788</v>
+        <v>-4.749453801624906</v>
       </c>
       <c r="D60">
-        <v>14.46234103041921</v>
+        <v>14.26854619837509</v>
       </c>
       <c r="E60">
-        <v>3.816000000000003</v>
+        <v>4.268000000000001</v>
       </c>
       <c r="F60">
-        <v>26.216</v>
+        <v>26.668</v>
       </c>
       <c r="G60">
         <v>7.65</v>
@@ -6207,37 +6207,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M60">
-        <v>5.264172800000001</v>
+        <v>5.3549344</v>
       </c>
       <c r="N60">
-        <v>-2.190506133333334</v>
+        <v>-2.281267733333334</v>
       </c>
       <c r="O60">
-        <v>-0.766677146666667</v>
+        <v>-0.7984437066666668</v>
       </c>
       <c r="P60">
-        <v>-1.423828986666667</v>
+        <v>-1.482824026666667</v>
       </c>
       <c r="Q60">
-        <v>-0.9808289866666673</v>
+        <v>-1.039824026666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1485803123799497</v>
+        <v>0.1510871492672656</v>
       </c>
       <c r="T60">
-        <v>1.882457516193583</v>
+        <v>1.928371114149524</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.2043594262964417</v>
+        <v>0.2008957072066715</v>
       </c>
       <c r="W60">
-        <v>0.1597646271996745</v>
+        <v>0.1604601419929004</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5838840751326906</v>
+        <v>0.5739877348762044</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1566172149753901</v>
+        <v>0.1581672149753901</v>
       </c>
       <c r="C61">
-        <v>-4.749453801624906</v>
+        <v>-5.390123621554036</v>
       </c>
       <c r="D61">
-        <v>14.26854619837509</v>
+        <v>14.07987637844596</v>
       </c>
       <c r="E61">
-        <v>4.268000000000001</v>
+        <v>4.720000000000002</v>
       </c>
       <c r="F61">
-        <v>26.668</v>
+        <v>27.12</v>
       </c>
       <c r="G61">
         <v>7.65</v>
@@ -6289,37 +6289,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M61">
-        <v>5.3549344</v>
+        <v>5.445696000000001</v>
       </c>
       <c r="N61">
-        <v>-2.281267733333334</v>
+        <v>-2.372029333333334</v>
       </c>
       <c r="O61">
-        <v>-0.7984437066666668</v>
+        <v>-0.830210266666667</v>
       </c>
       <c r="P61">
-        <v>-1.482824026666667</v>
+        <v>-1.541819066666667</v>
       </c>
       <c r="Q61">
-        <v>-1.039824026666667</v>
+        <v>-1.098819066666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1510871492672656</v>
+        <v>0.1537193279989472</v>
       </c>
       <c r="T61">
-        <v>1.928371114149524</v>
+        <v>1.976580392003262</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.2008957072066715</v>
+        <v>0.1975474454198936</v>
       </c>
       <c r="W61">
-        <v>0.1604601419929004</v>
+        <v>0.1611324729596854</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5739877348762044</v>
+        <v>0.5644212726282676</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1581672149753901</v>
+        <v>0.1597172149753901</v>
       </c>
       <c r="C62">
-        <v>-5.390123621554036</v>
+        <v>-6.025869076943412</v>
       </c>
       <c r="D62">
-        <v>14.07987637844596</v>
+        <v>13.89613092305659</v>
       </c>
       <c r="E62">
-        <v>4.720000000000002</v>
+        <v>5.172000000000004</v>
       </c>
       <c r="F62">
-        <v>27.12</v>
+        <v>27.572</v>
       </c>
       <c r="G62">
         <v>7.65</v>
@@ -6371,37 +6371,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M62">
-        <v>5.445696000000001</v>
+        <v>5.5364576</v>
       </c>
       <c r="N62">
-        <v>-2.372029333333334</v>
+        <v>-2.462790933333334</v>
       </c>
       <c r="O62">
-        <v>-0.830210266666667</v>
+        <v>-0.8619768266666668</v>
       </c>
       <c r="P62">
-        <v>-1.541819066666667</v>
+        <v>-1.600814106666667</v>
       </c>
       <c r="Q62">
-        <v>-1.098819066666667</v>
+        <v>-1.157814106666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1537193279989472</v>
+        <v>0.1564864902553305</v>
       </c>
       <c r="T62">
-        <v>1.976580392003262</v>
+        <v>2.027261940516167</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1975474454198936</v>
+        <v>0.1943089627080921</v>
       </c>
       <c r="W62">
-        <v>0.1611324729596854</v>
+        <v>0.1617827602882151</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5644212726282676</v>
+        <v>0.5551684648802633</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1597172149753901</v>
+        <v>0.1612672149753901</v>
       </c>
       <c r="C63">
-        <v>-6.025869076943412</v>
+        <v>-6.656880476316779</v>
       </c>
       <c r="D63">
-        <v>13.89613092305659</v>
+        <v>13.71711952368322</v>
       </c>
       <c r="E63">
-        <v>5.172000000000004</v>
+        <v>5.624000000000002</v>
       </c>
       <c r="F63">
-        <v>27.572</v>
+        <v>28.024</v>
       </c>
       <c r="G63">
         <v>7.65</v>
@@ -6453,37 +6453,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M63">
-        <v>5.5364576</v>
+        <v>5.627219200000001</v>
       </c>
       <c r="N63">
-        <v>-2.462790933333334</v>
+        <v>-2.553552533333334</v>
       </c>
       <c r="O63">
-        <v>-0.8619768266666668</v>
+        <v>-0.8937433866666669</v>
       </c>
       <c r="P63">
-        <v>-1.600814106666667</v>
+        <v>-1.659809146666667</v>
       </c>
       <c r="Q63">
-        <v>-1.157814106666667</v>
+        <v>-1.216809146666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1564864902553305</v>
+        <v>0.1593992926304708</v>
       </c>
       <c r="T63">
-        <v>2.027261940516167</v>
+        <v>2.080610938950803</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1943089627080921</v>
+        <v>0.1911749471805422</v>
       </c>
       <c r="W63">
-        <v>0.1617827602882151</v>
+        <v>0.1624120706061471</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5551684648802633</v>
+        <v>0.5462141348015492</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1612672149753901</v>
+        <v>0.1628172149753901</v>
       </c>
       <c r="C64">
-        <v>-6.656880476316779</v>
+        <v>-7.283338446620441</v>
       </c>
       <c r="D64">
-        <v>13.71711952368322</v>
+        <v>13.54266155337956</v>
       </c>
       <c r="E64">
-        <v>5.624000000000002</v>
+        <v>6.076000000000004</v>
       </c>
       <c r="F64">
-        <v>28.024</v>
+        <v>28.476</v>
       </c>
       <c r="G64">
         <v>7.65</v>
@@ -6535,37 +6535,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M64">
-        <v>5.627219200000001</v>
+        <v>5.7179808</v>
       </c>
       <c r="N64">
-        <v>-2.553552533333334</v>
+        <v>-2.644314133333334</v>
       </c>
       <c r="O64">
-        <v>-0.8937433866666669</v>
+        <v>-0.9255099466666667</v>
       </c>
       <c r="P64">
-        <v>-1.659809146666667</v>
+        <v>-1.718804186666667</v>
       </c>
       <c r="Q64">
-        <v>-1.216809146666667</v>
+        <v>-1.275804186666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1593992926304708</v>
+        <v>0.1624695437826457</v>
       </c>
       <c r="T64">
-        <v>2.080610938950803</v>
+        <v>2.136843667030554</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1911749471805422</v>
+        <v>0.1881404242094225</v>
       </c>
       <c r="W64">
-        <v>0.1624120706061471</v>
+        <v>0.163021402818748</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5462141348015492</v>
+        <v>0.5375440691697786</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1628172149753901</v>
+        <v>0.1643672149753901</v>
       </c>
       <c r="C65">
-        <v>-7.283338446620441</v>
+        <v>-7.905414541155753</v>
       </c>
       <c r="D65">
-        <v>13.54266155337956</v>
+        <v>13.37258545884425</v>
       </c>
       <c r="E65">
-        <v>6.076000000000004</v>
+        <v>6.528000000000002</v>
       </c>
       <c r="F65">
-        <v>28.476</v>
+        <v>28.928</v>
       </c>
       <c r="G65">
         <v>7.65</v>
@@ -6617,37 +6617,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M65">
-        <v>5.7179808</v>
+        <v>5.808742400000001</v>
       </c>
       <c r="N65">
-        <v>-2.644314133333334</v>
+        <v>-2.735075733333334</v>
       </c>
       <c r="O65">
-        <v>-0.9255099466666667</v>
+        <v>-0.9572765066666669</v>
       </c>
       <c r="P65">
-        <v>-1.718804186666667</v>
+        <v>-1.777799226666667</v>
       </c>
       <c r="Q65">
-        <v>-1.275804186666667</v>
+        <v>-1.334799226666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1624695437826457</v>
+        <v>0.1657103644432747</v>
       </c>
       <c r="T65">
-        <v>2.136843667030554</v>
+        <v>2.19620043555918</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1881404242094225</v>
+        <v>0.1852007300811503</v>
       </c>
       <c r="W65">
-        <v>0.163021402818748</v>
+        <v>0.163611693399705</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5375440691697786</v>
+        <v>0.5291449430890008</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1643672149753901</v>
+        <v>0.1659172149753901</v>
       </c>
       <c r="C66">
-        <v>-7.905414541155753</v>
+        <v>-8.523271802271363</v>
       </c>
       <c r="D66">
-        <v>13.37258545884425</v>
+        <v>13.20672819772864</v>
       </c>
       <c r="E66">
-        <v>6.528000000000002</v>
+        <v>6.980000000000004</v>
       </c>
       <c r="F66">
-        <v>28.928</v>
+        <v>29.38</v>
       </c>
       <c r="G66">
         <v>7.65</v>
@@ -6699,37 +6699,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M66">
-        <v>5.808742400000001</v>
+        <v>5.899504</v>
       </c>
       <c r="N66">
-        <v>-2.735075733333334</v>
+        <v>-2.825837333333334</v>
       </c>
       <c r="O66">
-        <v>-0.9572765066666669</v>
+        <v>-0.9890430666666667</v>
       </c>
       <c r="P66">
-        <v>-1.777799226666667</v>
+        <v>-1.836794266666667</v>
       </c>
       <c r="Q66">
-        <v>-1.334799226666667</v>
+        <v>-1.393794266666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1657103644432747</v>
+        <v>0.1691363748559397</v>
       </c>
       <c r="T66">
-        <v>2.19620043555918</v>
+        <v>2.258949019432301</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1852007300811503</v>
+        <v>0.1823514880799018</v>
       </c>
       <c r="W66">
-        <v>0.163611693399705</v>
+        <v>0.1641838211935557</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5291449430890008</v>
+        <v>0.5210042516568625</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1659172149753901</v>
+        <v>0.1674672149753901</v>
       </c>
       <c r="C67">
-        <v>-8.523271802271363</v>
+        <v>-9.137065282694643</v>
       </c>
       <c r="D67">
-        <v>13.20672819772864</v>
+        <v>13.04493471730536</v>
       </c>
       <c r="E67">
-        <v>6.980000000000004</v>
+        <v>7.432000000000006</v>
       </c>
       <c r="F67">
-        <v>29.38</v>
+        <v>29.832</v>
       </c>
       <c r="G67">
         <v>7.65</v>
@@ -6781,37 +6781,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M67">
-        <v>5.899504</v>
+        <v>5.990265600000001</v>
       </c>
       <c r="N67">
-        <v>-2.825837333333334</v>
+        <v>-2.916598933333334</v>
       </c>
       <c r="O67">
-        <v>-0.9890430666666667</v>
+        <v>-1.020809626666667</v>
       </c>
       <c r="P67">
-        <v>-1.836794266666667</v>
+        <v>-1.895789306666667</v>
       </c>
       <c r="Q67">
-        <v>-1.393794266666667</v>
+        <v>-1.452789306666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1691363748559397</v>
+        <v>0.1727639152928791</v>
       </c>
       <c r="T67">
-        <v>2.258949019432301</v>
+        <v>2.325388696474427</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1823514880799018</v>
+        <v>0.1795885867453579</v>
       </c>
       <c r="W67">
-        <v>0.1641838211935557</v>
+        <v>0.1647386117815322</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5210042516568625</v>
+        <v>0.5131102478438796</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1674672149753901</v>
+        <v>0.1690172149753901</v>
       </c>
       <c r="C68">
-        <v>-9.137065282694643</v>
+        <v>-9.746942529006517</v>
       </c>
       <c r="D68">
-        <v>13.04493471730536</v>
+        <v>12.88705747099348</v>
       </c>
       <c r="E68">
-        <v>7.432000000000006</v>
+        <v>7.884000000000004</v>
       </c>
       <c r="F68">
-        <v>29.832</v>
+        <v>30.284</v>
       </c>
       <c r="G68">
         <v>7.65</v>
@@ -6863,37 +6863,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M68">
-        <v>5.990265600000001</v>
+        <v>6.0810272</v>
       </c>
       <c r="N68">
-        <v>-2.916598933333334</v>
+        <v>-3.007360533333334</v>
       </c>
       <c r="O68">
-        <v>-1.020809626666667</v>
+        <v>-1.052576186666667</v>
       </c>
       <c r="P68">
-        <v>-1.895789306666667</v>
+        <v>-1.954784346666667</v>
       </c>
       <c r="Q68">
-        <v>-1.452789306666667</v>
+        <v>-1.511784346666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1727639152928791</v>
+        <v>0.1766113066653906</v>
       </c>
       <c r="T68">
-        <v>2.325388696474427</v>
+        <v>2.395855020610016</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1795885867453579</v>
+        <v>0.1769081600775167</v>
       </c>
       <c r="W68">
-        <v>0.1647386117815322</v>
+        <v>0.1652768414564346</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5131102478438796</v>
+        <v>0.505451885935762</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1690172149753901</v>
+        <v>0.1952287994100142</v>
       </c>
       <c r="C69">
-        <v>-9.746942529006517</v>
+        <v>-12.3883541748747</v>
       </c>
       <c r="D69">
-        <v>12.88705747099348</v>
+        <v>10.69764582512531</v>
       </c>
       <c r="E69">
-        <v>7.884000000000004</v>
+        <v>8.336000000000006</v>
       </c>
       <c r="F69">
-        <v>30.284</v>
+        <v>30.736</v>
       </c>
       <c r="G69">
         <v>7.65</v>
@@ -6945,45 +6945,45 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M69">
-        <v>6.0810272</v>
+        <v>7.247548800000001</v>
       </c>
       <c r="N69">
-        <v>-3.007360533333334</v>
+        <v>-4.173882133333334</v>
       </c>
       <c r="O69">
-        <v>-1.052576186666667</v>
+        <v>-1.460858746666667</v>
       </c>
       <c r="P69">
-        <v>-1.954784346666667</v>
+        <v>-2.713023386666667</v>
       </c>
       <c r="Q69">
-        <v>-1.511784346666667</v>
+        <v>-2.270023386666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1766113066653906</v>
+        <v>0.1833916113568844</v>
       </c>
       <c r="T69">
-        <v>2.395855020610016</v>
+        <v>2.520038682179378</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1769081600775167</v>
+        <v>0.1484340931010127</v>
       </c>
       <c r="W69">
-        <v>0.1652768414564346</v>
+        <v>0.2007992408467812</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.505451885935762</v>
+        <v>0.4240974088600364</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1952287994100142</v>
+        <v>0.1971287994100142</v>
       </c>
       <c r="C70">
-        <v>-12.3883541748747</v>
+        <v>-12.97049289583204</v>
       </c>
       <c r="D70">
-        <v>10.69764582512531</v>
+        <v>10.56750710416797</v>
       </c>
       <c r="E70">
-        <v>8.336000000000006</v>
+        <v>8.788000000000007</v>
       </c>
       <c r="F70">
-        <v>30.736</v>
+        <v>31.18800000000001</v>
       </c>
       <c r="G70">
         <v>7.65</v>
@@ -7027,37 +7027,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M70">
-        <v>7.247548800000001</v>
+        <v>7.354130400000002</v>
       </c>
       <c r="N70">
-        <v>-4.173882133333334</v>
+        <v>-4.280463733333335</v>
       </c>
       <c r="O70">
-        <v>-1.460858746666667</v>
+        <v>-1.498162306666667</v>
       </c>
       <c r="P70">
-        <v>-2.713023386666667</v>
+        <v>-2.782301426666668</v>
       </c>
       <c r="Q70">
-        <v>-2.270023386666667</v>
+        <v>-2.339301426666668</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1833916113568844</v>
+        <v>0.1878300504329129</v>
       </c>
       <c r="T70">
-        <v>2.520038682179378</v>
+        <v>2.601330252572261</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1484340931010127</v>
+        <v>0.1462828743604183</v>
       </c>
       <c r="W70">
-        <v>0.2007992408467812</v>
+        <v>0.2013064982258134</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4240974088600364</v>
+        <v>0.4179510696011953</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1971287994100142</v>
+        <v>0.1990287994100142</v>
       </c>
       <c r="C71">
-        <v>-12.97049289583204</v>
+        <v>-13.54950335234703</v>
       </c>
       <c r="D71">
-        <v>10.56750710416797</v>
+        <v>10.44049664765298</v>
       </c>
       <c r="E71">
-        <v>8.788000000000007</v>
+        <v>9.240000000000006</v>
       </c>
       <c r="F71">
-        <v>31.18800000000001</v>
+        <v>31.64</v>
       </c>
       <c r="G71">
         <v>7.65</v>
@@ -7109,37 +7109,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M71">
-        <v>7.354130400000002</v>
+        <v>7.460712000000001</v>
       </c>
       <c r="N71">
-        <v>-4.280463733333335</v>
+        <v>-4.387045333333335</v>
       </c>
       <c r="O71">
-        <v>-1.498162306666667</v>
+        <v>-1.535465866666667</v>
       </c>
       <c r="P71">
-        <v>-2.782301426666668</v>
+        <v>-2.851579466666668</v>
       </c>
       <c r="Q71">
-        <v>-2.339301426666668</v>
+        <v>-2.408579466666668</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1878300504329129</v>
+        <v>0.1925643854473433</v>
       </c>
       <c r="T71">
-        <v>2.601330252572261</v>
+        <v>2.688041260991337</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1462828743604183</v>
+        <v>0.1441931190124124</v>
       </c>
       <c r="W71">
-        <v>0.2013064982258134</v>
+        <v>0.2017992625368732</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4179510696011953</v>
+        <v>0.4119803400354639</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1990287994100142</v>
+        <v>0.2009287994100142</v>
       </c>
       <c r="C72">
-        <v>-13.54950335234703</v>
+        <v>-14.12549700030145</v>
       </c>
       <c r="D72">
-        <v>10.44049664765298</v>
+        <v>10.31650299969856</v>
       </c>
       <c r="E72">
-        <v>9.240000000000006</v>
+        <v>9.692000000000007</v>
       </c>
       <c r="F72">
-        <v>31.64</v>
+        <v>32.09200000000001</v>
       </c>
       <c r="G72">
         <v>7.65</v>
@@ -7191,37 +7191,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M72">
-        <v>7.460712000000001</v>
+        <v>7.567293600000002</v>
       </c>
       <c r="N72">
-        <v>-4.387045333333335</v>
+        <v>-4.493626933333335</v>
       </c>
       <c r="O72">
-        <v>-1.535465866666667</v>
+        <v>-1.572769426666667</v>
       </c>
       <c r="P72">
-        <v>-2.851579466666668</v>
+        <v>-2.920857506666668</v>
       </c>
       <c r="Q72">
-        <v>-2.408579466666668</v>
+        <v>-2.477857506666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1925643854473433</v>
+        <v>0.1976252263248379</v>
       </c>
       <c r="T72">
-        <v>2.688041260991337</v>
+        <v>2.780732338956556</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1441931190124124</v>
+        <v>0.1421622300122375</v>
       </c>
       <c r="W72">
-        <v>0.2017992625368732</v>
+        <v>0.2022781461631144</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4119803400354639</v>
+        <v>0.4061778000349644</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2009287994100142</v>
+        <v>0.2028287994100142</v>
       </c>
       <c r="C73">
-        <v>-14.12549700030144</v>
+        <v>-14.6985800630212</v>
       </c>
       <c r="D73">
-        <v>10.31650299969855</v>
+        <v>10.1954199369788</v>
       </c>
       <c r="E73">
-        <v>9.692</v>
+        <v>10.14400000000001</v>
       </c>
       <c r="F73">
-        <v>32.092</v>
+        <v>32.544</v>
       </c>
       <c r="G73">
         <v>7.65</v>
@@ -7273,37 +7273,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M73">
-        <v>7.5672936</v>
+        <v>7.673875200000001</v>
       </c>
       <c r="N73">
-        <v>-4.493626933333333</v>
+        <v>-4.600208533333335</v>
       </c>
       <c r="O73">
-        <v>-1.572769426666667</v>
+        <v>-1.610072986666667</v>
       </c>
       <c r="P73">
-        <v>-2.920857506666667</v>
+        <v>-2.990135546666668</v>
       </c>
       <c r="Q73">
-        <v>-2.477857506666667</v>
+        <v>-2.547135546666668</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1976252263248379</v>
+        <v>0.2030475558364392</v>
       </c>
       <c r="T73">
-        <v>2.780732338956554</v>
+        <v>2.880044208205003</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1421622300122375</v>
+        <v>0.1401877545954009</v>
       </c>
       <c r="W73">
-        <v>0.2022781461631144</v>
+        <v>0.2027437274664045</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4061778000349645</v>
+        <v>0.4005364417011454</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2028287994100142</v>
+        <v>0.2047287994100142</v>
       </c>
       <c r="C74">
-        <v>-14.6985800630212</v>
+        <v>-15.26885383478232</v>
       </c>
       <c r="D74">
-        <v>10.1954199369788</v>
+        <v>10.07714616521768</v>
       </c>
       <c r="E74">
-        <v>10.14400000000001</v>
+        <v>10.596</v>
       </c>
       <c r="F74">
-        <v>32.544</v>
+        <v>32.996</v>
       </c>
       <c r="G74">
         <v>7.65</v>
@@ -7355,37 +7355,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M74">
-        <v>7.673875200000001</v>
+        <v>7.780456800000001</v>
       </c>
       <c r="N74">
-        <v>-4.600208533333335</v>
+        <v>-4.706790133333334</v>
       </c>
       <c r="O74">
-        <v>-1.610072986666667</v>
+        <v>-1.647376546666667</v>
       </c>
       <c r="P74">
-        <v>-2.990135546666668</v>
+        <v>-3.059413586666667</v>
       </c>
       <c r="Q74">
-        <v>-2.547135546666668</v>
+        <v>-2.616413586666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2030475558364392</v>
+        <v>0.208871539385937</v>
       </c>
       <c r="T74">
-        <v>2.880044208205003</v>
+        <v>2.986712512212595</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1401877545954009</v>
+        <v>0.1382673743954639</v>
       </c>
       <c r="W74">
-        <v>0.2027437274664045</v>
+        <v>0.2031965531175496</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4005364417011454</v>
+        <v>0.395049641129897</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2047287994100142</v>
+        <v>0.2066287994100142</v>
       </c>
       <c r="C75">
-        <v>-15.26885383478232</v>
+        <v>-15.83641496343387</v>
       </c>
       <c r="D75">
-        <v>10.07714616521768</v>
+        <v>9.961585036566127</v>
       </c>
       <c r="E75">
-        <v>10.596</v>
+        <v>11.048</v>
       </c>
       <c r="F75">
-        <v>32.996</v>
+        <v>33.448</v>
       </c>
       <c r="G75">
         <v>7.65</v>
@@ -7437,37 +7437,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M75">
-        <v>7.780456800000001</v>
+        <v>7.887038400000001</v>
       </c>
       <c r="N75">
-        <v>-4.706790133333334</v>
+        <v>-4.813371733333334</v>
       </c>
       <c r="O75">
-        <v>-1.647376546666667</v>
+        <v>-1.684680106666667</v>
       </c>
       <c r="P75">
-        <v>-3.059413586666667</v>
+        <v>-3.128691626666667</v>
       </c>
       <c r="Q75">
-        <v>-2.616413586666667</v>
+        <v>-2.685691626666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.208871539385937</v>
+        <v>0.2151435216700115</v>
       </c>
       <c r="T75">
-        <v>2.986712512212595</v>
+        <v>3.101586070374618</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1382673743954639</v>
+        <v>0.1363988963630928</v>
       </c>
       <c r="W75">
-        <v>0.2031965531175496</v>
+        <v>0.2036371402375827</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.395049641129897</v>
+        <v>0.3897111324659794</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2066287994100142</v>
+        <v>0.2085287994100142</v>
       </c>
       <c r="C76">
-        <v>-15.83641496343387</v>
+        <v>-16.4013557137953</v>
       </c>
       <c r="D76">
-        <v>9.961585036566127</v>
+        <v>9.848644286204701</v>
       </c>
       <c r="E76">
-        <v>11.048</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="F76">
-        <v>33.448</v>
+        <v>33.90000000000001</v>
       </c>
       <c r="G76">
         <v>7.65</v>
@@ -7519,37 +7519,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M76">
-        <v>7.887038400000001</v>
+        <v>7.993620000000002</v>
       </c>
       <c r="N76">
-        <v>-4.813371733333334</v>
+        <v>-4.919953333333336</v>
       </c>
       <c r="O76">
-        <v>-1.684680106666667</v>
+        <v>-1.721983666666667</v>
       </c>
       <c r="P76">
-        <v>-3.128691626666667</v>
+        <v>-3.197969666666668</v>
       </c>
       <c r="Q76">
-        <v>-2.685691626666667</v>
+        <v>-2.754969666666668</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2151435216700115</v>
+        <v>0.221917262536812</v>
       </c>
       <c r="T76">
-        <v>3.101586070374618</v>
+        <v>3.225649513189603</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1363988963630928</v>
+        <v>0.1345802444115849</v>
       </c>
       <c r="W76">
-        <v>0.2036371402375827</v>
+        <v>0.2040659783677483</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3897111324659794</v>
+        <v>0.3845149840330996</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2085287994100142</v>
+        <v>0.2104287994100142</v>
       </c>
       <c r="C77">
-        <v>-16.4013557137953</v>
+        <v>-16.9637642133368</v>
       </c>
       <c r="D77">
-        <v>9.848644286204701</v>
+        <v>9.738235786663205</v>
       </c>
       <c r="E77">
-        <v>11.50000000000001</v>
+        <v>11.95200000000001</v>
       </c>
       <c r="F77">
-        <v>33.90000000000001</v>
+        <v>34.352</v>
       </c>
       <c r="G77">
         <v>7.65</v>
@@ -7601,37 +7601,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M77">
-        <v>7.993620000000002</v>
+        <v>8.100201600000002</v>
       </c>
       <c r="N77">
-        <v>-4.919953333333336</v>
+        <v>-5.026534933333336</v>
       </c>
       <c r="O77">
-        <v>-1.721983666666667</v>
+        <v>-1.759287226666667</v>
       </c>
       <c r="P77">
-        <v>-3.197969666666668</v>
+        <v>-3.267247706666669</v>
       </c>
       <c r="Q77">
-        <v>-2.754969666666668</v>
+        <v>-2.824247706666668</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.221917262536812</v>
+        <v>0.2292554818091792</v>
       </c>
       <c r="T77">
-        <v>3.225649513189603</v>
+        <v>3.360051576239171</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1345802444115849</v>
+        <v>0.1328094517219587</v>
       </c>
       <c r="W77">
-        <v>0.2040659783677483</v>
+        <v>0.2044835312839622</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3845149840330996</v>
+        <v>0.3794555763484535</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2104287994100142</v>
+        <v>0.2123287994100142</v>
       </c>
       <c r="C78">
-        <v>-16.9637642133368</v>
+        <v>-17.52372468151762</v>
       </c>
       <c r="D78">
-        <v>9.738235786663205</v>
+        <v>9.630275318482381</v>
       </c>
       <c r="E78">
-        <v>11.95200000000001</v>
+        <v>12.404</v>
       </c>
       <c r="F78">
-        <v>34.352</v>
+        <v>34.804</v>
       </c>
       <c r="G78">
         <v>7.65</v>
@@ -7683,37 +7683,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M78">
-        <v>8.100201600000002</v>
+        <v>8.2067832</v>
       </c>
       <c r="N78">
-        <v>-5.026534933333336</v>
+        <v>-5.133116533333334</v>
       </c>
       <c r="O78">
-        <v>-1.759287226666667</v>
+        <v>-1.796590786666667</v>
       </c>
       <c r="P78">
-        <v>-3.267247706666669</v>
+        <v>-3.336525746666667</v>
       </c>
       <c r="Q78">
-        <v>-2.824247706666668</v>
+        <v>-2.893525746666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2292554818091792</v>
+        <v>0.2372318071052304</v>
       </c>
       <c r="T78">
-        <v>3.360051576239171</v>
+        <v>3.506140775206091</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1328094517219587</v>
+        <v>0.1310846536476476</v>
       </c>
       <c r="W78">
-        <v>0.2044835312839622</v>
+        <v>0.2048902386698847</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3794555763484535</v>
+        <v>0.3745275818504218</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2123287994100142</v>
+        <v>0.2142287994100142</v>
       </c>
       <c r="C79">
-        <v>-17.52372468151762</v>
+        <v>-18.08131764403674</v>
       </c>
       <c r="D79">
-        <v>9.630275318482381</v>
+        <v>9.524682355963261</v>
       </c>
       <c r="E79">
-        <v>12.404</v>
+        <v>12.856</v>
       </c>
       <c r="F79">
-        <v>34.804</v>
+        <v>35.256</v>
       </c>
       <c r="G79">
         <v>7.65</v>
@@ -7765,37 +7765,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M79">
-        <v>8.2067832</v>
+        <v>8.3133648</v>
       </c>
       <c r="N79">
-        <v>-5.133116533333334</v>
+        <v>-5.239698133333334</v>
       </c>
       <c r="O79">
-        <v>-1.796590786666667</v>
+        <v>-1.833894346666667</v>
       </c>
       <c r="P79">
-        <v>-3.336525746666667</v>
+        <v>-3.405803786666667</v>
       </c>
       <c r="Q79">
-        <v>-2.893525746666667</v>
+        <v>-2.962803786666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2372318071052304</v>
+        <v>0.2459332528827409</v>
       </c>
       <c r="T79">
-        <v>3.506140775206091</v>
+        <v>3.665510810442731</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1310846536476476</v>
+        <v>0.1294040811649855</v>
       </c>
       <c r="W79">
-        <v>0.2048902386698847</v>
+        <v>0.2052865176612964</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3745275818504218</v>
+        <v>0.3697259461856728</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2142287994100142</v>
+        <v>0.2161287994100143</v>
       </c>
       <c r="C80">
-        <v>-18.08131764403674</v>
+        <v>-18.63662013314112</v>
       </c>
       <c r="D80">
-        <v>9.524682355963261</v>
+        <v>9.421379866858887</v>
       </c>
       <c r="E80">
-        <v>12.856</v>
+        <v>13.30800000000001</v>
       </c>
       <c r="F80">
-        <v>35.256</v>
+        <v>35.70800000000001</v>
       </c>
       <c r="G80">
         <v>7.65</v>
@@ -7847,37 +7847,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M80">
-        <v>8.3133648</v>
+        <v>8.419946400000002</v>
       </c>
       <c r="N80">
-        <v>-5.239698133333334</v>
+        <v>-5.346279733333336</v>
       </c>
       <c r="O80">
-        <v>-1.833894346666667</v>
+        <v>-1.871197906666668</v>
       </c>
       <c r="P80">
-        <v>-3.405803786666667</v>
+        <v>-3.475081826666669</v>
       </c>
       <c r="Q80">
-        <v>-2.962803786666667</v>
+        <v>-3.032081826666669</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2459332528827409</v>
+        <v>0.2554634077819191</v>
       </c>
       <c r="T80">
-        <v>3.665510810442731</v>
+        <v>3.840058944273339</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1294040811649855</v>
+        <v>0.1277660548211249</v>
       </c>
       <c r="W80">
-        <v>0.2052865176612964</v>
+        <v>0.2056727642731788</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3697259461856728</v>
+        <v>0.3650458709174996</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2161287994100143</v>
+        <v>0.2180287994100142</v>
       </c>
       <c r="C81">
-        <v>-18.63662013314112</v>
+        <v>-19.1897058750389</v>
       </c>
       <c r="D81">
-        <v>9.421379866858887</v>
+        <v>9.320294124961103</v>
       </c>
       <c r="E81">
-        <v>13.30800000000001</v>
+        <v>13.76000000000001</v>
       </c>
       <c r="F81">
-        <v>35.70800000000001</v>
+        <v>36.16</v>
       </c>
       <c r="G81">
         <v>7.65</v>
@@ -7929,37 +7929,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M81">
-        <v>8.419946400000002</v>
+        <v>8.526528000000001</v>
       </c>
       <c r="N81">
-        <v>-5.346279733333336</v>
+        <v>-5.452861333333335</v>
       </c>
       <c r="O81">
-        <v>-1.871197906666668</v>
+        <v>-1.908501466666667</v>
       </c>
       <c r="P81">
-        <v>-3.475081826666669</v>
+        <v>-3.544359866666667</v>
       </c>
       <c r="Q81">
-        <v>-3.032081826666669</v>
+        <v>-3.101359866666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2554634077819191</v>
+        <v>0.265946578171015</v>
       </c>
       <c r="T81">
-        <v>3.840058944273339</v>
+        <v>4.032061891487005</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1277660548211249</v>
+        <v>0.1261689791358608</v>
       </c>
       <c r="W81">
-        <v>0.2056727642731788</v>
+        <v>0.206049354719764</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3650458709174996</v>
+        <v>0.3604827975310309</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2180287994100142</v>
+        <v>0.2199287994100142</v>
       </c>
       <c r="C82">
-        <v>-19.1897058750389</v>
+        <v>-19.74064546537577</v>
       </c>
       <c r="D82">
-        <v>9.320294124961103</v>
+        <v>9.221354534624234</v>
       </c>
       <c r="E82">
-        <v>13.76000000000001</v>
+        <v>14.212</v>
       </c>
       <c r="F82">
-        <v>36.16</v>
+        <v>36.612</v>
       </c>
       <c r="G82">
         <v>7.65</v>
@@ -8011,37 +8011,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M82">
-        <v>8.526528000000001</v>
+        <v>8.633109600000001</v>
       </c>
       <c r="N82">
-        <v>-5.452861333333335</v>
+        <v>-5.559442933333335</v>
       </c>
       <c r="O82">
-        <v>-1.908501466666667</v>
+        <v>-1.945805026666667</v>
       </c>
       <c r="P82">
-        <v>-3.544359866666667</v>
+        <v>-3.613637906666668</v>
       </c>
       <c r="Q82">
-        <v>-3.101359866666667</v>
+        <v>-3.170637906666668</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.265946578171015</v>
+        <v>0.2775332401800158</v>
       </c>
       <c r="T82">
-        <v>4.032061891487005</v>
+        <v>4.244275675249479</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1261689791358608</v>
+        <v>0.1246113374181341</v>
       </c>
       <c r="W82">
-        <v>0.206049354719764</v>
+        <v>0.206416646636804</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3604827975310309</v>
+        <v>0.3560323926232404</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2199287994100142</v>
+        <v>0.2218287994100142</v>
       </c>
       <c r="C83">
-        <v>-19.74064546537577</v>
+        <v>-20.28950653365195</v>
       </c>
       <c r="D83">
-        <v>9.221354534624234</v>
+        <v>9.124493466348056</v>
       </c>
       <c r="E83">
-        <v>14.212</v>
+        <v>14.66400000000001</v>
       </c>
       <c r="F83">
-        <v>36.612</v>
+        <v>37.06400000000001</v>
       </c>
       <c r="G83">
         <v>7.65</v>
@@ -8093,37 +8093,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M83">
-        <v>8.633109600000001</v>
+        <v>8.739691200000003</v>
       </c>
       <c r="N83">
-        <v>-5.559442933333335</v>
+        <v>-5.666024533333337</v>
       </c>
       <c r="O83">
-        <v>-1.945805026666667</v>
+        <v>-1.983108586666668</v>
       </c>
       <c r="P83">
-        <v>-3.613637906666668</v>
+        <v>-3.682915946666669</v>
       </c>
       <c r="Q83">
-        <v>-3.170637906666668</v>
+        <v>-3.239915946666669</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2775332401800158</v>
+        <v>0.2904073090789056</v>
       </c>
       <c r="T83">
-        <v>4.244275675249479</v>
+        <v>4.480068768318895</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1246113374181341</v>
+        <v>0.1230916869618154</v>
       </c>
       <c r="W83">
-        <v>0.206416646636804</v>
+        <v>0.2067749802144039</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3560323926232404</v>
+        <v>0.3516905341766154</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2218287994100142</v>
+        <v>0.2237287994100142</v>
       </c>
       <c r="C84">
-        <v>-20.28950653365195</v>
+        <v>-20.8363538973848</v>
       </c>
       <c r="D84">
-        <v>9.124493466348056</v>
+        <v>9.029646102615203</v>
       </c>
       <c r="E84">
-        <v>14.66400000000001</v>
+        <v>15.11600000000001</v>
       </c>
       <c r="F84">
-        <v>37.06400000000001</v>
+        <v>37.51600000000001</v>
       </c>
       <c r="G84">
         <v>7.65</v>
@@ -8175,37 +8175,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M84">
-        <v>8.739691200000003</v>
+        <v>8.846272800000001</v>
       </c>
       <c r="N84">
-        <v>-5.666024533333337</v>
+        <v>-5.772606133333335</v>
       </c>
       <c r="O84">
-        <v>-1.983108586666668</v>
+        <v>-2.020412146666667</v>
       </c>
       <c r="P84">
-        <v>-3.682915946666669</v>
+        <v>-3.752193986666668</v>
       </c>
       <c r="Q84">
-        <v>-3.239915946666669</v>
+        <v>-3.309193986666668</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2904073090789056</v>
+        <v>0.3047959743188412</v>
       </c>
       <c r="T84">
-        <v>4.480068768318895</v>
+        <v>4.74360222527883</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1230916869618154</v>
+        <v>0.1216086545887815</v>
       </c>
       <c r="W84">
-        <v>0.2067749802144039</v>
+        <v>0.2071246792479653</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3516905341766154</v>
+        <v>0.34745329882509</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2237287994100142</v>
+        <v>0.2256287994100142</v>
       </c>
       <c r="C85">
-        <v>-20.8363538973848</v>
+        <v>-21.38124970675539</v>
       </c>
       <c r="D85">
-        <v>9.029646102615203</v>
+        <v>8.936750293244609</v>
       </c>
       <c r="E85">
-        <v>15.11600000000001</v>
+        <v>15.568</v>
       </c>
       <c r="F85">
-        <v>37.51600000000001</v>
+        <v>37.968</v>
       </c>
       <c r="G85">
         <v>7.65</v>
@@ -8257,37 +8257,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M85">
-        <v>8.846272800000001</v>
+        <v>8.952854400000001</v>
       </c>
       <c r="N85">
-        <v>-5.772606133333335</v>
+        <v>-5.879187733333335</v>
       </c>
       <c r="O85">
-        <v>-2.020412146666667</v>
+        <v>-2.057715706666667</v>
       </c>
       <c r="P85">
-        <v>-3.752193986666668</v>
+        <v>-3.821472026666668</v>
       </c>
       <c r="Q85">
-        <v>-3.309193986666668</v>
+        <v>-3.378472026666668</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3047959743188412</v>
+        <v>0.3209832227137689</v>
       </c>
       <c r="T85">
-        <v>4.74360222527883</v>
+        <v>5.040077364358758</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1216086545887815</v>
+        <v>0.1201609325103436</v>
       </c>
       <c r="W85">
-        <v>0.2071246792479653</v>
+        <v>0.207466052114061</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.34745329882509</v>
+        <v>0.3433169500295532</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2256287994100142</v>
+        <v>0.2275287994100142</v>
       </c>
       <c r="C86">
-        <v>-21.38124970675539</v>
+        <v>-21.92425358041729</v>
       </c>
       <c r="D86">
-        <v>8.936750293244613</v>
+        <v>8.845746419582706</v>
       </c>
       <c r="E86">
-        <v>15.568</v>
+        <v>16.02</v>
       </c>
       <c r="F86">
-        <v>37.968</v>
+        <v>38.42</v>
       </c>
       <c r="G86">
         <v>7.65</v>
@@ -8339,37 +8339,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M86">
-        <v>8.952854400000001</v>
+        <v>9.059436000000002</v>
       </c>
       <c r="N86">
-        <v>-5.879187733333335</v>
+        <v>-5.985769333333335</v>
       </c>
       <c r="O86">
-        <v>-2.057715706666667</v>
+        <v>-2.095019266666667</v>
       </c>
       <c r="P86">
-        <v>-3.821472026666668</v>
+        <v>-3.890750066666668</v>
       </c>
       <c r="Q86">
-        <v>-3.378472026666668</v>
+        <v>-3.447750066666668</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3209832227137687</v>
+        <v>0.3393287708946865</v>
       </c>
       <c r="T86">
-        <v>5.040077364358755</v>
+        <v>5.376082521982672</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1201609325103436</v>
+        <v>0.1187472744808102</v>
       </c>
       <c r="W86">
-        <v>0.207466052114061</v>
+        <v>0.2077993926774249</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3433169500295532</v>
+        <v>0.3392779270880291</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2275287994100142</v>
+        <v>0.2294287994100142</v>
       </c>
       <c r="C87">
-        <v>-21.92425358041729</v>
+        <v>-22.46542273309138</v>
       </c>
       <c r="D87">
-        <v>8.845746419582706</v>
+        <v>8.756577266908618</v>
       </c>
       <c r="E87">
-        <v>16.02</v>
+        <v>16.472</v>
       </c>
       <c r="F87">
-        <v>38.42</v>
+        <v>38.872</v>
       </c>
       <c r="G87">
         <v>7.65</v>
@@ -8421,37 +8421,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M87">
-        <v>9.059436000000002</v>
+        <v>9.1660176</v>
       </c>
       <c r="N87">
-        <v>-5.985769333333335</v>
+        <v>-6.092350933333334</v>
       </c>
       <c r="O87">
-        <v>-2.095019266666667</v>
+        <v>-2.132322826666667</v>
       </c>
       <c r="P87">
-        <v>-3.890750066666668</v>
+        <v>-3.960028106666667</v>
       </c>
       <c r="Q87">
-        <v>-3.447750066666668</v>
+        <v>-3.517028106666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3393287708946865</v>
+        <v>0.3602951116728785</v>
       </c>
       <c r="T87">
-        <v>5.376082521982672</v>
+        <v>5.760088416410006</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1187472744808102</v>
+        <v>0.1173664922194054</v>
       </c>
       <c r="W87">
-        <v>0.2077993926774249</v>
+        <v>0.2081249811346642</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3392779270880291</v>
+        <v>0.3353328349125869</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2294287994100142</v>
+        <v>0.2313287994100142</v>
       </c>
       <c r="C88">
-        <v>-22.46542273309138</v>
+        <v>-23.00481209552026</v>
       </c>
       <c r="D88">
-        <v>8.756577266908618</v>
+        <v>8.66918790447974</v>
       </c>
       <c r="E88">
-        <v>16.472</v>
+        <v>16.92400000000001</v>
       </c>
       <c r="F88">
-        <v>38.872</v>
+        <v>39.32400000000001</v>
       </c>
       <c r="G88">
         <v>7.65</v>
@@ -8503,37 +8503,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M88">
-        <v>9.1660176</v>
+        <v>9.272599200000002</v>
       </c>
       <c r="N88">
-        <v>-6.092350933333334</v>
+        <v>-6.198932533333336</v>
       </c>
       <c r="O88">
-        <v>-2.132322826666667</v>
+        <v>-2.169626386666667</v>
       </c>
       <c r="P88">
-        <v>-3.960028106666667</v>
+        <v>-4.029306146666668</v>
       </c>
       <c r="Q88">
-        <v>-3.517028106666667</v>
+        <v>-3.586306146666668</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3602951116728785</v>
+        <v>0.384487043340023</v>
       </c>
       <c r="T88">
-        <v>5.760088416410006</v>
+        <v>6.203172140749238</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1173664922194054</v>
+        <v>0.1160174520789525</v>
       </c>
       <c r="W88">
-        <v>0.2081249811346642</v>
+        <v>0.208443084799783</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3353328349125869</v>
+        <v>0.3314784345112928</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2313287994100142</v>
+        <v>0.2332287994100142</v>
       </c>
       <c r="C89">
-        <v>-23.00481209552026</v>
+        <v>-23.54247442731101</v>
       </c>
       <c r="D89">
-        <v>8.66918790447974</v>
+        <v>8.583525572688989</v>
       </c>
       <c r="E89">
-        <v>16.92400000000001</v>
+        <v>17.376</v>
       </c>
       <c r="F89">
-        <v>39.32400000000001</v>
+        <v>39.776</v>
       </c>
       <c r="G89">
         <v>7.65</v>
@@ -8585,37 +8585,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M89">
-        <v>9.272599200000002</v>
+        <v>9.3791808</v>
       </c>
       <c r="N89">
-        <v>-6.198932533333336</v>
+        <v>-6.305514133333334</v>
       </c>
       <c r="O89">
-        <v>-2.169626386666667</v>
+        <v>-2.206929946666667</v>
       </c>
       <c r="P89">
-        <v>-4.029306146666668</v>
+        <v>-4.098584186666667</v>
       </c>
       <c r="Q89">
-        <v>-3.586306146666668</v>
+        <v>-3.655584186666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.384487043340023</v>
+        <v>0.4127109636183582</v>
       </c>
       <c r="T89">
-        <v>6.203172140749238</v>
+        <v>6.72010315247834</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1160174520789525</v>
+        <v>0.1146990719416917</v>
       </c>
       <c r="W89">
-        <v>0.208443084799783</v>
+        <v>0.2087539588361491</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3314784345112928</v>
+        <v>0.327711634119119</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2332287994100142</v>
+        <v>0.2351287994100142</v>
       </c>
       <c r="C90">
-        <v>-23.54247442731101</v>
+        <v>-24.07846042315316</v>
       </c>
       <c r="D90">
-        <v>8.583525572688989</v>
+        <v>8.499539576846837</v>
       </c>
       <c r="E90">
-        <v>17.376</v>
+        <v>17.828</v>
       </c>
       <c r="F90">
-        <v>39.776</v>
+        <v>40.228</v>
       </c>
       <c r="G90">
         <v>7.65</v>
@@ -8667,37 +8667,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M90">
-        <v>9.3791808</v>
+        <v>9.4857624</v>
       </c>
       <c r="N90">
-        <v>-6.305514133333334</v>
+        <v>-6.412095733333334</v>
       </c>
       <c r="O90">
-        <v>-2.206929946666667</v>
+        <v>-2.244233506666667</v>
       </c>
       <c r="P90">
-        <v>-4.098584186666667</v>
+        <v>-4.167862226666667</v>
       </c>
       <c r="Q90">
-        <v>-3.655584186666667</v>
+        <v>-3.724862226666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4127109636183582</v>
+        <v>0.4460665057654817</v>
       </c>
       <c r="T90">
-        <v>6.72010315247834</v>
+        <v>7.331021620885462</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1146990719416917</v>
+        <v>0.1134103183243693</v>
       </c>
       <c r="W90">
-        <v>0.2087539588361491</v>
+        <v>0.2090578469391137</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.327711634119119</v>
+        <v>0.3240294809267693</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2351287994100142</v>
+        <v>0.2370287994100142</v>
       </c>
       <c r="C91">
-        <v>-24.07846042315316</v>
+        <v>-24.61281881286135</v>
       </c>
       <c r="D91">
-        <v>8.499539576846837</v>
+        <v>8.417181187138654</v>
       </c>
       <c r="E91">
-        <v>17.828</v>
+        <v>18.28000000000001</v>
       </c>
       <c r="F91">
-        <v>40.228</v>
+        <v>40.68000000000001</v>
       </c>
       <c r="G91">
         <v>7.65</v>
@@ -8749,37 +8749,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M91">
-        <v>9.4857624</v>
+        <v>9.592344000000002</v>
       </c>
       <c r="N91">
-        <v>-6.412095733333334</v>
+        <v>-6.518677333333336</v>
       </c>
       <c r="O91">
-        <v>-2.244233506666667</v>
+        <v>-2.281537066666667</v>
       </c>
       <c r="P91">
-        <v>-4.167862226666667</v>
+        <v>-4.237140266666669</v>
       </c>
       <c r="Q91">
-        <v>-3.724862226666667</v>
+        <v>-3.794140266666669</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4460665057654817</v>
+        <v>0.48609315634203</v>
       </c>
       <c r="T91">
-        <v>7.331021620885462</v>
+        <v>8.06412378297401</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1134103183243693</v>
+        <v>0.1121502036763207</v>
       </c>
       <c r="W91">
-        <v>0.2090578469391137</v>
+        <v>0.2093549819731236</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3240294809267693</v>
+        <v>0.3204291533609163</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2370287994100142</v>
+        <v>0.2389287994100142</v>
       </c>
       <c r="C92">
-        <v>-24.61281881286135</v>
+        <v>-25.14559645565743</v>
       </c>
       <c r="D92">
-        <v>8.417181187138654</v>
+        <v>8.336403544342577</v>
       </c>
       <c r="E92">
-        <v>18.28000000000001</v>
+        <v>18.73200000000001</v>
       </c>
       <c r="F92">
-        <v>40.68000000000001</v>
+        <v>41.13200000000001</v>
       </c>
       <c r="G92">
         <v>7.65</v>
@@ -8831,37 +8831,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M92">
-        <v>9.592344000000002</v>
+        <v>9.698925600000001</v>
       </c>
       <c r="N92">
-        <v>-6.518677333333336</v>
+        <v>-6.625258933333335</v>
       </c>
       <c r="O92">
-        <v>-2.281537066666667</v>
+        <v>-2.318840626666667</v>
       </c>
       <c r="P92">
-        <v>-4.237140266666669</v>
+        <v>-4.306418306666668</v>
       </c>
       <c r="Q92">
-        <v>-3.794140266666669</v>
+        <v>-3.863418306666668</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.48609315634203</v>
+        <v>0.5350146181578112</v>
       </c>
       <c r="T92">
-        <v>8.06412378297401</v>
+        <v>8.96013753663779</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1121502036763207</v>
+        <v>0.1109177838557018</v>
       </c>
       <c r="W92">
-        <v>0.2093549819731236</v>
+        <v>0.2096455865668255</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3204291533609163</v>
+        <v>0.3169079538734337</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2389287994100142</v>
+        <v>0.2408287994100142</v>
       </c>
       <c r="C93">
-        <v>-25.14559645565743</v>
+        <v>-25.67683842907542</v>
       </c>
       <c r="D93">
-        <v>8.336403544342577</v>
+        <v>8.257161570924588</v>
       </c>
       <c r="E93">
-        <v>18.73200000000001</v>
+        <v>19.184</v>
       </c>
       <c r="F93">
-        <v>41.13200000000001</v>
+        <v>41.584</v>
       </c>
       <c r="G93">
         <v>7.65</v>
@@ -8913,37 +8913,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M93">
-        <v>9.698925600000001</v>
+        <v>9.805507200000001</v>
       </c>
       <c r="N93">
-        <v>-6.625258933333335</v>
+        <v>-6.731840533333335</v>
       </c>
       <c r="O93">
-        <v>-2.318840626666667</v>
+        <v>-2.356144186666667</v>
       </c>
       <c r="P93">
-        <v>-4.306418306666668</v>
+        <v>-4.375696346666668</v>
       </c>
       <c r="Q93">
-        <v>-3.863418306666668</v>
+        <v>-3.932696346666668</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5350146181578112</v>
+        <v>0.5961664454275377</v>
       </c>
       <c r="T93">
-        <v>8.96013753663779</v>
+        <v>10.08015472871752</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1109177838557018</v>
+        <v>0.1097121557703137</v>
       </c>
       <c r="W93">
-        <v>0.2096455865668255</v>
+        <v>0.20992987366936</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3169079538734337</v>
+        <v>0.3134633022008965</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2408287994100142</v>
+        <v>0.2427287994100142</v>
       </c>
       <c r="C94">
-        <v>-25.67683842907542</v>
+        <v>-26.20658811284362</v>
       </c>
       <c r="D94">
-        <v>8.257161570924588</v>
+        <v>8.179411887156379</v>
       </c>
       <c r="E94">
-        <v>19.184</v>
+        <v>19.636</v>
       </c>
       <c r="F94">
-        <v>41.584</v>
+        <v>42.036</v>
       </c>
       <c r="G94">
         <v>7.65</v>
@@ -8995,37 +8995,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M94">
-        <v>9.805507200000001</v>
+        <v>9.912088800000001</v>
       </c>
       <c r="N94">
-        <v>-6.731840533333335</v>
+        <v>-6.838422133333335</v>
       </c>
       <c r="O94">
-        <v>-2.356144186666667</v>
+        <v>-2.393447746666667</v>
       </c>
       <c r="P94">
-        <v>-4.375696346666668</v>
+        <v>-4.444974386666668</v>
       </c>
       <c r="Q94">
-        <v>-3.932696346666668</v>
+        <v>-4.001974386666668</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5961664454275377</v>
+        <v>0.6747902233457574</v>
       </c>
       <c r="T94">
-        <v>10.08015472871752</v>
+        <v>11.52017683282002</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1097121557703137</v>
+        <v>0.108532455170633</v>
       </c>
       <c r="W94">
-        <v>0.20992987366936</v>
+        <v>0.2102080470707648</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3134633022008965</v>
+        <v>0.3100927290589514</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2427287994100142</v>
+        <v>0.2446287994100142</v>
       </c>
       <c r="C95">
-        <v>-26.20658811284362</v>
+        <v>-26.73488726807198</v>
       </c>
       <c r="D95">
-        <v>8.179411887156379</v>
+        <v>8.10311273192803</v>
       </c>
       <c r="E95">
-        <v>19.636</v>
+        <v>20.08800000000001</v>
       </c>
       <c r="F95">
-        <v>42.036</v>
+        <v>42.48800000000001</v>
       </c>
       <c r="G95">
         <v>7.65</v>
@@ -9077,37 +9077,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M95">
-        <v>9.912088800000001</v>
+        <v>10.0186704</v>
       </c>
       <c r="N95">
-        <v>-6.838422133333335</v>
+        <v>-6.945003733333335</v>
       </c>
       <c r="O95">
-        <v>-2.393447746666667</v>
+        <v>-2.430751306666667</v>
       </c>
       <c r="P95">
-        <v>-4.444974386666668</v>
+        <v>-4.514252426666668</v>
       </c>
       <c r="Q95">
-        <v>-4.001974386666668</v>
+        <v>-4.071252426666669</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6747902233457574</v>
+        <v>0.7796219272367171</v>
       </c>
       <c r="T95">
-        <v>11.52017683282002</v>
+        <v>13.44020630495669</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.108532455170633</v>
+        <v>0.1073778545837113</v>
       </c>
       <c r="W95">
-        <v>0.2102080470707648</v>
+        <v>0.2104803018891609</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3100927290589514</v>
+        <v>0.3067938702391753</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2446287994100142</v>
+        <v>0.2465287994100142</v>
       </c>
       <c r="C96">
-        <v>-26.73488726807198</v>
+        <v>-27.26177611204823</v>
       </c>
       <c r="D96">
-        <v>8.10311273192803</v>
+        <v>8.02822388795177</v>
       </c>
       <c r="E96">
-        <v>20.08800000000001</v>
+        <v>20.54000000000001</v>
       </c>
       <c r="F96">
-        <v>42.48800000000001</v>
+        <v>42.94</v>
       </c>
       <c r="G96">
         <v>7.65</v>
@@ -9159,37 +9159,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M96">
-        <v>10.0186704</v>
+        <v>10.125252</v>
       </c>
       <c r="N96">
-        <v>-6.945003733333335</v>
+        <v>-7.051585333333335</v>
       </c>
       <c r="O96">
-        <v>-2.430751306666667</v>
+        <v>-2.468054866666667</v>
       </c>
       <c r="P96">
-        <v>-4.514252426666668</v>
+        <v>-4.583530466666668</v>
       </c>
       <c r="Q96">
-        <v>-4.071252426666669</v>
+        <v>-4.140530466666668</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7796219272367171</v>
+        <v>0.926386312684061</v>
       </c>
       <c r="T96">
-        <v>13.44020630495669</v>
+        <v>16.12824756594804</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1073778545837113</v>
+        <v>0.106247561377567</v>
       </c>
       <c r="W96">
-        <v>0.2104803018891609</v>
+        <v>0.2107468250271697</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3067938702391753</v>
+        <v>0.3035644610787629</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2465287994100142</v>
+        <v>0.2484287994100142</v>
       </c>
       <c r="C97">
-        <v>-27.26177611204823</v>
+        <v>-27.78729338892462</v>
       </c>
       <c r="D97">
-        <v>8.02822388795177</v>
+        <v>7.954706611075381</v>
       </c>
       <c r="E97">
-        <v>20.54000000000001</v>
+        <v>20.992</v>
       </c>
       <c r="F97">
-        <v>42.94</v>
+        <v>43.392</v>
       </c>
       <c r="G97">
         <v>7.65</v>
@@ -9241,37 +9241,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M97">
-        <v>10.125252</v>
+        <v>10.2318336</v>
       </c>
       <c r="N97">
-        <v>-7.051585333333335</v>
+        <v>-7.158166933333336</v>
       </c>
       <c r="O97">
-        <v>-2.468054866666667</v>
+        <v>-2.505358426666667</v>
       </c>
       <c r="P97">
-        <v>-4.583530466666668</v>
+        <v>-4.652808506666668</v>
       </c>
       <c r="Q97">
-        <v>-4.140530466666668</v>
+        <v>-4.209808506666668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.926386312684061</v>
+        <v>1.146532890855077</v>
       </c>
       <c r="T97">
-        <v>16.12824756594804</v>
+        <v>20.16030945743506</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.106247561377567</v>
+        <v>0.1051408159465507</v>
       </c>
       <c r="W97">
-        <v>0.2107468250271697</v>
+        <v>0.2110077955998034</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3035644610787629</v>
+        <v>0.300402331275859</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2484287994100142</v>
+        <v>0.2503287994100142</v>
       </c>
       <c r="C98">
-        <v>-27.78729338892462</v>
+        <v>-28.31147643655587</v>
       </c>
       <c r="D98">
-        <v>7.954706611075381</v>
+        <v>7.882523563444134</v>
       </c>
       <c r="E98">
-        <v>20.992</v>
+        <v>21.444</v>
       </c>
       <c r="F98">
-        <v>43.392</v>
+        <v>43.844</v>
       </c>
       <c r="G98">
         <v>7.65</v>
@@ -9323,37 +9323,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M98">
-        <v>10.2318336</v>
+        <v>10.3384152</v>
       </c>
       <c r="N98">
-        <v>-7.158166933333336</v>
+        <v>-7.264748533333334</v>
       </c>
       <c r="O98">
-        <v>-2.505358426666667</v>
+        <v>-2.542661986666667</v>
       </c>
       <c r="P98">
-        <v>-4.652808506666668</v>
+        <v>-4.722086546666667</v>
       </c>
       <c r="Q98">
-        <v>-4.209808506666668</v>
+        <v>-4.279086546666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.146532890855074</v>
+        <v>1.513443854473432</v>
       </c>
       <c r="T98">
-        <v>20.160309457435</v>
+        <v>26.88041260991334</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1051408159465507</v>
+        <v>0.1040568900089574</v>
       </c>
       <c r="W98">
-        <v>0.2110077955998034</v>
+        <v>0.2112633853358879</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.300402331275859</v>
+        <v>0.2973054000255925</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2503287994100142</v>
+        <v>0.2522287994100142</v>
       </c>
       <c r="C99">
-        <v>-28.31147643655587</v>
+        <v>-28.83436124973096</v>
       </c>
       <c r="D99">
-        <v>7.882523563444134</v>
+        <v>7.811638750269037</v>
       </c>
       <c r="E99">
-        <v>21.444</v>
+        <v>21.896</v>
       </c>
       <c r="F99">
-        <v>43.844</v>
+        <v>44.296</v>
       </c>
       <c r="G99">
         <v>7.65</v>
@@ -9405,37 +9405,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M99">
-        <v>10.3384152</v>
+        <v>10.4449968</v>
       </c>
       <c r="N99">
-        <v>-7.264748533333334</v>
+        <v>-7.371330133333334</v>
       </c>
       <c r="O99">
-        <v>-2.542661986666667</v>
+        <v>-2.579965546666667</v>
       </c>
       <c r="P99">
-        <v>-4.722086546666667</v>
+        <v>-4.791364586666667</v>
       </c>
       <c r="Q99">
-        <v>-4.279086546666667</v>
+        <v>-4.348364586666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.513443854473432</v>
+        <v>2.247265781710147</v>
       </c>
       <c r="T99">
-        <v>26.88041260991334</v>
+        <v>40.32061891487</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1040568900089574</v>
+        <v>0.102995085008866</v>
       </c>
       <c r="W99">
-        <v>0.2112633853358879</v>
+        <v>0.2115137589549094</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2973054000255925</v>
+        <v>0.2942716714539028</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2522287994100142</v>
+        <v>0.2541287994100142</v>
       </c>
       <c r="C100">
-        <v>-28.83436124973096</v>
+        <v>-29.35598254002356</v>
       </c>
       <c r="D100">
-        <v>7.811638750269037</v>
+        <v>7.742017459976442</v>
       </c>
       <c r="E100">
-        <v>21.896</v>
+        <v>22.34800000000001</v>
       </c>
       <c r="F100">
-        <v>44.296</v>
+        <v>44.748</v>
       </c>
       <c r="G100">
         <v>7.65</v>
@@ -9487,37 +9487,37 @@
         <v>3.073666666666667</v>
       </c>
       <c r="M100">
-        <v>10.4449968</v>
+        <v>10.5515784</v>
       </c>
       <c r="N100">
-        <v>-7.371330133333334</v>
+        <v>-7.477911733333336</v>
       </c>
       <c r="O100">
-        <v>-2.579965546666667</v>
+        <v>-2.617269106666667</v>
       </c>
       <c r="P100">
-        <v>-4.791364586666667</v>
+        <v>-4.860642626666669</v>
       </c>
       <c r="Q100">
-        <v>-4.348364586666667</v>
+        <v>-4.41764262666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.247265781710147</v>
+        <v>4.448731563420295</v>
       </c>
       <c r="T100">
-        <v>40.32061891487</v>
+        <v>80.64123782974001</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.102995085008866</v>
+        <v>0.101954730614837</v>
       </c>
       <c r="W100">
-        <v>0.2115137589549094</v>
+        <v>0.2117590745210214</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2942716714539028</v>
+        <v>0.2912992303281058</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2541287994100142</v>
-      </c>
-      <c r="C101">
-        <v>-29.35598254002356</v>
-      </c>
-      <c r="D101">
-        <v>7.742017459976442</v>
-      </c>
-      <c r="E101">
-        <v>22.34800000000001</v>
-      </c>
-      <c r="F101">
-        <v>44.748</v>
-      </c>
-      <c r="G101">
-        <v>7.65</v>
-      </c>
-      <c r="H101">
-        <v>22.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.516666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.443</v>
-      </c>
-      <c r="L101">
-        <v>3.073666666666667</v>
-      </c>
-      <c r="M101">
-        <v>10.5515784</v>
-      </c>
-      <c r="N101">
-        <v>-7.477911733333336</v>
-      </c>
-      <c r="O101">
-        <v>-2.617269106666667</v>
-      </c>
-      <c r="P101">
-        <v>-4.860642626666669</v>
-      </c>
-      <c r="Q101">
-        <v>-4.41764262666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.448731563420295</v>
-      </c>
-      <c r="T101">
-        <v>80.64123782974001</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.101954730614837</v>
-      </c>
-      <c r="W101">
-        <v>0.2117590745210214</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2912992303281058</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
